--- a/workspaces/btc_daily_14days/williams_r/wr_spread_7_14.xlsx
+++ b/workspaces/btc_daily_14days/williams_r/wr_spread_7_14.xlsx
@@ -575,46 +575,46 @@
         <v>32</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.6315616797900248</v>
+        <v>0.6289086908361696</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.271282874815661</v>
+        <v>5.254450370951311</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.751007191345536</v>
+        <v>1.745236289092759</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.26382250830802</v>
+        <v>11.22720577459035</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.599693538216457</v>
+        <v>7.574531191750111</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.899509061015266</v>
+        <v>7.873207862630551</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.94618752365998</v>
+        <v>10.91037680184665</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.4809380311417</v>
+        <v>10.44665158652776</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.42240935252509</v>
+        <v>10.38839300119364</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.441143552363982</v>
+        <v>6.419776573041403</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.02796418643553977</v>
+        <v>-0.02853372900260354</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.126993444498652</v>
+        <v>-3.117569264984724</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.549249796302313</v>
+        <v>-3.538442412484578</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.970682525222401</v>
+        <v>2.960447582576819</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.82677165354179</v>
+        <v>-5.808642438129446</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.562297580371428</v>
+        <v>2.553940570947539</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.837869485520251</v>
+        <v>8.809160337789649</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.3063948341897</v>
+        <v>12.26585357722258</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.760686591876592</v>
+        <v>1.753963487679002</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.953327496618357</v>
+        <v>-7.928920311830979</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-8.040145129699667</v>
+        <v>-8.015290658123703</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-8.510081934132842</v>
+        <v>-8.483664633712458</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-8.573291975845656</v>
+        <v>-8.546585335241296</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-9.427383135059927</v>
+        <v>-9.39791526958841</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.951875881412015</v>
+        <v>-2.943026887175961</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.260665269159979</v>
+        <v>-6.240992569593274</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.683732013934929</v>
+        <v>-6.662652227681512</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.434484290792774</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.5677861695859434</v>
+        <v>0.5807471212737383</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.038620395934167</v>
+        <v>3.093448673460429</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.602529327602511</v>
+        <v>0.6155842005617842</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7332376322763636</v>
+        <v>0.7526721945795174</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.848338984230338</v>
+        <v>-1.875123267188407</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.601198763016811</v>
+        <v>1.635439630750881</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.610554399648578</v>
+        <v>-4.687560503655185</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.025740947842642</v>
+        <v>-3.074930825278088</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.00302894057176</v>
+        <v>1.024898031430112</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.875876460221349</v>
+        <v>-1.905284520210024</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.076723621699209</v>
+        <v>-2.110282561919313</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.179978737293851</v>
+        <v>-8.323217738047006</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-10.64100210619093</v>
+        <v>-10.82823804203424</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-8.353218971639578</v>
+        <v>-8.497885750758883</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.8805350944035268</v>
+        <v>-0.8783638110159302</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.800480491756375</v>
+        <v>8.773281070001104</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>18.09006405900587</v>
+        <v>18.03426683408769</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13.38283398023741</v>
+        <v>13.34072996611905</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.618220263548125</v>
+        <v>9.587800402972206</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.072344921677356</v>
+        <v>5.055747867603401</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.218647071066592</v>
+        <v>8.192818831690161</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.137529580220871</v>
+        <v>6.118067779924431</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.462296891678562</v>
+        <v>4.447894622656932</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.611545911842875</v>
+        <v>3.599882618660864</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.407213393491809</v>
+        <v>3.396284947151955</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.408865686806251</v>
+        <v>-1.404598216242114</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.300554877067491</v>
+        <v>-8.275051711729077</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.6696268388093</v>
+        <v>-9.640358869036767</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.222979590237784</v>
+        <v>4.276687189098084</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11.56969087286424</v>
+        <v>11.71425426279252</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>17.15103391240393</v>
+        <v>17.36647309847835</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.817580060822102</v>
+        <v>9.945142347157294</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.597963035479786</v>
+        <v>8.709188550329273</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.87919053197403</v>
+        <v>12.03010806947418</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13.29406603331271</v>
+        <v>13.46131285506601</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>12.83724040490872</v>
+        <v>12.99849699272885</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.295938442084804</v>
+        <v>8.401495130163831</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>13.44099602221428</v>
+        <v>13.60888556406471</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.756025333179153</v>
+        <v>8.86601984999885</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.803120761025987</v>
+        <v>5.874139867207639</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.391507712751988</v>
+        <v>5.455561532899765</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.631738817983276</v>
+        <v>8.736962734089857</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>82</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.712950515331926</v>
+        <v>-3.702811072541486</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-10.20516373986076</v>
+        <v>-10.17666459801407</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.061559301997058</v>
+        <v>-2.057692513409634</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.1520072910184</v>
+        <v>-3.145070034769653</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.470483016022328</v>
+        <v>-2.465134507907862</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.61375882250303</v>
+        <v>-4.60220134989676</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1835300968232829</v>
+        <v>0.1812700969711756</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.50525231499536</v>
+        <v>-1.502469315463181</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3452801073970164</v>
+        <v>-0.3456374219946596</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.246661675412099</v>
+        <v>1.241574212397111</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.402530321796739</v>
+        <v>-1.399537213295226</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.591443429822185</v>
+        <v>-2.584157914182889</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6543392934863235</v>
+        <v>0.6526454337852172</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3176132836230749</v>
+        <v>-0.3169914418148423</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>86</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.819019715559079</v>
+        <v>-4.805117335277856</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.87257128489955</v>
+        <v>2.863341932595631</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.011673981794068</v>
+        <v>-1.010764089039768</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2823522644593837</v>
+        <v>0.2793566677345325</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9071286040653206</v>
+        <v>0.9026411983283609</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.532262366476346</v>
+        <v>3.520036719799826</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.207618790886251</v>
+        <v>-1.205830240063001</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.310515202262934</v>
+        <v>5.293084989975803</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.921532533778795</v>
+        <v>2.911409899620246</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.4241732701608</v>
+        <v>-1.421522130186602</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.865950394103407</v>
+        <v>1.859325910187991</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.065887223461559</v>
+        <v>3.056621824678757</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.811016550262025</v>
+        <v>3.799825127279568</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6020980910738771</v>
+        <v>-0.6005989290525093</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13.16312733635591</v>
+        <v>13.26075619150203</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.482177691216556</v>
+        <v>4.517450212317236</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.441778262293823</v>
+        <v>-2.454648639102224</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.30302192597329</v>
+        <v>-1.30714547107528</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.207437343158269</v>
+        <v>2.228411874929314</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.523097140007252</v>
+        <v>4.561388939359048</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.474044180514497</v>
+        <v>7.533651469283789</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8.023894935236541</v>
+        <v>8.088097468423896</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.932338970155861</v>
+        <v>4.972838459256991</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.067626438194246</v>
+        <v>2.086706879319287</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.866159970600208</v>
+        <v>1.882943589596358</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.915587386694618</v>
+        <v>2.937949409379726</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.487380024974627</v>
+        <v>1.498565168582729</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.774017655685114</v>
+        <v>4.809937378493764</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.906561679789839</v>
+        <v>1.919208156403229</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.695889256772439</v>
+        <v>2.712873780199807</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.100876970005018</v>
+        <v>-4.119654580949522</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.370575580784255</v>
+        <v>-2.379509645509337</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2925304411054981</v>
+        <v>0.2979881214615929</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.5901981106360239</v>
+        <v>0.5977829492597877</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.93901153165114</v>
+        <v>4.970346628195614</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.476189993383194</v>
+        <v>4.505491795158768</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.423199127990991</v>
+        <v>8.472869849553632</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.377418319452154</v>
+        <v>4.404440593683468</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.176127499056697</v>
+        <v>4.201411540475704</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.808424780569204</v>
+        <v>1.819330367768885</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.391867573310542</v>
+        <v>1.3998171759389</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.243997245969155</v>
+        <v>3.262866937413918</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.187882764654105</v>
+        <v>-3.219985333093199</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-9.983009621703587</v>
+        <v>-10.09584687365587</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-8.986180360468175</v>
+        <v>-9.087225533582654</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.707135535422857</v>
+        <v>-5.767302108710439</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.239134142916214</v>
+        <v>-6.304747737821046</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.086200875720863</v>
+        <v>-1.08898192549033</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.994527834752603</v>
+        <v>3.042539302582341</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.923182821543548</v>
+        <v>3.983193023314293</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.47571700800281</v>
+        <v>2.517597270398767</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.201722382931699</v>
+        <v>7.296892493791198</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.22248767475763</v>
+        <v>4.28052323075741</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.34896266675544</v>
+        <v>6.427993002963049</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.546154228502829</v>
+        <v>4.601905414523777</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.487579646144667</v>
+        <v>5.55727856849105</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>183</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.151370422959296</v>
+        <v>2.145709903433776</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.099547452299909</v>
+        <v>-1.097375251374949</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.58731233375989</v>
+        <v>-2.581892311848165</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.096403463447473</v>
+        <v>-4.088265156579297</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.274168940814974</v>
+        <v>-6.261293492874394</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.337382740803861</v>
+        <v>-4.329580909955055</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.42211645807626</v>
+        <v>-4.414920284062326</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.610704479115739</v>
+        <v>-1.610052451178497</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.155655004750592</v>
+        <v>2.148201365625489</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.305713193765392</v>
+        <v>1.300316228249081</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5403061903302984</v>
+        <v>-0.5409907688725681</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.337484600968679</v>
+        <v>-4.329037325455658</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1672669815131727</v>
+        <v>0.166170736808823</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6770181323816686</v>
+        <v>-0.676847499391819</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>244</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8540940579148923</v>
+        <v>-0.8533134810972314</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4031847881372457</v>
+        <v>0.4020392457594966</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.221192115180656</v>
+        <v>-1.218279354484274</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.777913476443238</v>
+        <v>1.773030281565674</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.449032328792775</v>
+        <v>-2.443517012299267</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.331918259929765</v>
+        <v>-1.330241254260407</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.686419895190909</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.753881968078623</v>
+        <v>-4.745523036526166</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.636306193563058</v>
+        <v>-5.625993999246056</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.617086370706986</v>
+        <v>-3.611360855187009</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.592267842808319</v>
+        <v>-2.5880851032842</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.314478551308305</v>
+        <v>0.3129096540708929</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.98120509607346</v>
+        <v>-2.97483983678093</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.963689902449929</v>
+        <v>-3.955536023981978</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.920574418643525</v>
+        <v>2.923517114636041</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.582886155997741</v>
+        <v>2.585199653387392</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.869546111821535</v>
+        <v>1.871080777186087</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.184914131367144</v>
+        <v>-1.185580714664241</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.142906691777249</v>
+        <v>1.143870554378211</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.425893408723653</v>
+        <v>-1.426619428952669</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.355614912220631</v>
+        <v>1.357381173400739</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.697833580747748</v>
+        <v>1.700160281413957</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.912414133240013</v>
+        <v>2.915790919280816</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.109624161219351</v>
+        <v>1.11148209441594</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.9068005727503632</v>
+        <v>0.9081973952928593</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.62333387995821</v>
+        <v>0.6242029187193836</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4338630404677986</v>
+        <v>-0.4341236967969095</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.46148807381055</v>
+        <v>-1.462475740108303</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>954</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.08253685270472033</v>
+        <v>-0.08563964970929305</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.274823253928936</v>
+        <v>-1.271729479305861</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.355226551720506</v>
+        <v>-1.350713105365315</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4912207985679302</v>
+        <v>-0.4905675781458996</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8199984077700719</v>
+        <v>-0.8173945484635325</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1063743475556294</v>
+        <v>0.1042143894198588</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3361060390883921</v>
+        <v>0.3313489884321825</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2882098520469611</v>
+        <v>0.2821896679780167</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.01850001108721955</v>
+        <v>0.01289810453155837</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.637353959344253</v>
+        <v>0.6301313294820403</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.27281541234899</v>
+        <v>1.264719618089636</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.833037750180466</v>
+        <v>1.824370655769478</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.778536475547973</v>
+        <v>2.767918922230493</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.926040486623826</v>
+        <v>2.914588043791333</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>324</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.210265383493692</v>
+        <v>1.198138577259655</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.14190164707265</v>
+        <v>1.136876479865222</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.450736644179791</v>
+        <v>4.43287318927748</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.803211999009477</v>
+        <v>1.79391003768697</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8957030432231861</v>
+        <v>-0.8901877443427182</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.06739690797658</v>
+        <v>-3.057022454229653</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.769414575866222</v>
+        <v>-3.759888629639349</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149290345400388</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.754670626143238</v>
+        <v>-2.75297477500439</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.388331849761151</v>
+        <v>-6.370209141755247</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.359763750148133</v>
+        <v>-5.345188990202921</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.947874145266923</v>
+        <v>-5.929128672537509</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.683139943964413</v>
+        <v>-6.660500510848166</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.745145254370264</v>
+        <v>-6.723194392733248</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>219</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4745982094703862</v>
+        <v>0.4604613544021277</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.223733394361453</v>
+        <v>-0.2236982426289273</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.490986940137859</v>
+        <v>3.469474079876527</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.251377059046717</v>
+        <v>2.234908472392405</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.712955843974548</v>
+        <v>1.706751563196526</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.923639790822584</v>
+        <v>2.905946752154513</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.122011096381407</v>
+        <v>5.086929667393228</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.284964683901329</v>
+        <v>3.257921284400688</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>6.428389915616393</v>
+        <v>6.379921400012577</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.95568266204981</v>
+        <v>6.908783650959762</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>6.300112562100217</v>
+        <v>6.257238096838599</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.131558797701928</v>
+        <v>3.109287783426012</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.087833779203301</v>
+        <v>4.062017073285396</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.426320054281241</v>
+        <v>3.402799180748957</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>167</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.195184434281039</v>
+        <v>3.157191781397692</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.0092035499407</v>
+        <v>-1.997419888348233</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.386346905139362</v>
+        <v>2.362998202763137</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.917797642537273</v>
+        <v>1.896558630965679</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.175783613093856</v>
+        <v>3.157342947874461</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.119588820447909</v>
+        <v>-0.1247628462554431</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3944798574893937</v>
+        <v>0.3756347437737588</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6715059365018234</v>
+        <v>-0.6839818973219849</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.726146608036942</v>
+        <v>-3.728373752207169</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.380020744427974</v>
+        <v>-6.359109019309798</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.988880632336574</v>
+        <v>-5.969121564656689</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.564777012019086</v>
+        <v>-6.532741998531741</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.993753096508847</v>
+        <v>-6.957659317465129</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.350110852211003</v>
+        <v>-7.312756010239042</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>120</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8059727828748535</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.728321400159103</v>
+        <v>1.71609088921246</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.166786026895842</v>
+        <v>2.136648279989409</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.297039159503385</v>
+        <v>2.265243974636917</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.425284611097844</v>
+        <v>3.398282184332501</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.389393215480176</v>
+        <v>0.3784955608930147</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.362007168458732</v>
+        <v>-1.374382705226985</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.504142766093054</v>
+        <v>1.470690143266552</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2185951140640796</v>
+        <v>-0.2481671502151528</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.942892776007213</v>
+        <v>3.893267532634006</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4375227115509333</v>
+        <v>-0.4526152139851902</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>8.804419165150563</v>
+        <v>8.731761709290922</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.198665754014954</v>
+        <v>4.163138349555929</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.77787043892306</v>
+        <v>2.752114249242062</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>123</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.791114525318484</v>
+        <v>2.727415550258705</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.057589692842036</v>
+        <v>6.002153773065267</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>9.727761636651948</v>
+        <v>9.618983104436836</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.67102289934069</v>
+        <v>10.55270512885995</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>11.75861794443112</v>
+        <v>11.64719523452537</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.804027361821632</v>
+        <v>8.713822341648317</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.467261124224102</v>
+        <v>5.38923952000706</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.748045205117442</v>
+        <v>1.700275564408862</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.06817330741306904</v>
+        <v>0.02530781557018713</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0347872346476521</v>
+        <v>0.002161542182498977</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.54729646304007</v>
+        <v>5.473134717114718</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.227205029862191</v>
+        <v>7.142319996447071</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.714588473332249</v>
+        <v>2.679466000814479</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.151521466856444</v>
+        <v>2.122032948429009</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>91</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.2538144270427765</v>
+        <v>0.1928654000431607</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.334548506386206</v>
+        <v>6.255753277950525</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.567410587291448</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.674328536792721</v>
+        <v>1.605510184778936</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>7.729313915127214</v>
+        <v>7.618463509636022</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>8.026755852842804</v>
+        <v>7.911265434978297</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.645318838867233</v>
+        <v>4.54697777076354</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.277036538986827</v>
+        <v>5.175041248684309</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.033140078392371</v>
+        <v>2.943706338051776</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.498580519373817</v>
+        <v>5.397276661285453</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.995740165634814</v>
+        <v>1.930971725678894</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.039405231624841</v>
+        <v>1.976906038690892</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.041908752923931</v>
+        <v>5.959324914609276</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.306251978457041</v>
+        <v>6.222810219938104</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>92</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-10.10213397238389</v>
+        <v>-10.05839712986473</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.278924976652526</v>
+        <v>-6.231926952327321</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.673793683249116</v>
+        <v>-6.662969335126959</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-7.630497072380713</v>
+        <v>-7.610536789411938</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.908048722235456</v>
+        <v>-4.904856927276349</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.613798579478946</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-10.13012311048777</v>
+        <v>-10.0833795046014</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-9.510349987530134</v>
+        <v>-9.468486589878268</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-10.66592919134138</v>
+        <v>-10.62019241600229</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-6.074720993795992</v>
+        <v>-6.071504927759477</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.191165052120098</v>
+        <v>-5.191726496604446</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-7.350779423210007</v>
+        <v>-7.321073779137677</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.503954145164627</v>
+        <v>-4.487642018434201</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.054942321415673</v>
+        <v>-2.066726330468086</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>75</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4934383202099752</v>
+        <v>-0.5719056553907294</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.5616547334924746</v>
+        <v>0.5280828350056055</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1667860268958847</v>
+        <v>0.08237782131784854</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.104275274685172</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-6.908048722235534</v>
+        <v>-6.874436952135262</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.610606784519831</v>
+        <v>-2.644218554620089</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.69534050179211</v>
+        <v>-6.679670957723964</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.170809432759725</v>
+        <v>2.059527759746828</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.466732839159</v>
+        <v>3.32519308366949</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.973622841140433</v>
+        <v>3.831807402367573</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.787369895698774</v>
+        <v>3.655825512098353</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.548854116225179</v>
+        <v>-1.591601650021296</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.112125433337312</v>
+        <v>5.980446413691539</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.03864613922228</v>
+        <v>4.918780915908727</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-14.25814420256292</v>
+        <v>-14.12914814715267</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.163835462585993</v>
+        <v>-1.181267361965801</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.029292404476706</v>
+        <v>-3.093043350779823</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.899039271869206</v>
+        <v>-2.962790218172323</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.895348338401696</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.669430313931592</v>
+        <v>-1.733430287368662</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.818164004640941</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.633112135867769</v>
+        <v>-6.637096570011714</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.165117525398422</v>
+        <v>-8.162613917072903</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.065090991467194</v>
+        <v>-6.090764932417166</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.273024757006702</v>
+        <v>-6.283779835196135</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.770547397118158</v>
+        <v>-4.774872656633768</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-14.15646851414971</v>
+        <v>-13.98936420857586</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-7.941851768097351</v>
+        <v>-7.885140652718718</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-10.55795444924223</v>
+        <v>-10.65427728881735</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.717915158980681</v>
+        <v>-5.780612570922287</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.725687091383776</v>
+        <v>-7.731641594193839</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4690821702560299</v>
+        <v>0.613741562054301</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.156467406796814</v>
+        <v>3.29079398489521</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.841006118705984</v>
+        <v>1.988642761909297</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.369175627240153</v>
+        <v>3.546935049365153</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3238142231542014</v>
+        <v>-0.2008712533691934</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.3769652567877628</v>
+        <v>0.5332875497340979</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.806734169515622</v>
+        <v>3.005350424690732</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.024832970193167</v>
+        <v>1.174921262060842</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.35911077085612</v>
+        <v>4.535164219174966</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.52274169646339</v>
+        <v>10.76935456888311</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.445503801772617</v>
+        <v>3.585447582575398</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>52</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5703613971330483</v>
+        <v>-0.6346418591934224</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.510372682210416</v>
+        <v>5.386318506352346</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6537267936169258</v>
+        <v>-0.7699534593348645</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.446550584086431</v>
+        <v>-2.560168079757553</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.784258970072152</v>
+        <v>2.638145447455422</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-10.3798375537506</v>
+        <v>-10.33500726840229</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-12.3876481940998</v>
+        <v>-12.31554022189935</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-9.008677746727457</v>
+        <v>-8.997292277432635</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.14660070983286</v>
+        <v>-7.193328573396947</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.987252315090856</v>
+        <v>-8.025146634170554</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.256472471540036</v>
+        <v>-6.300332120662802</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-4.283684934567894</v>
+        <v>-4.333361309382788</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.76914614858228</v>
+        <v>-2.818119903546993</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.513058228160645</v>
+        <v>-2.568398571270755</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>48</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.756561679790025</v>
+        <v>3.56186507204994</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06165473349241068</v>
+        <v>-0.01080903462352722</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.750119360229213</v>
+        <v>1.517200105570822</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-4.369627507163287</v>
+        <v>-4.503406771377335</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>1.147254670024424</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.639393215480169</v>
+        <v>1.444696607740084</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-6.778673835125439</v>
+        <v>-6.790220259715284</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-9.329190567240282</v>
+        <v>-9.304505107772179</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-11.47352378675588</v>
+        <v>-11.45082909014818</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-8.143160097906673</v>
+        <v>-8.198448926748569</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.244289235672589</v>
+        <v>-6.312515356530305</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.218178073611853</v>
+        <v>-6.252632827137333</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-15.19481632369577</v>
+        <v>-14.99760708303422</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.28440260469052</v>
+        <v>-4.331219084091266</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.211387038158676</v>
+        <v>-1.385571827728086</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-18.20757603573833</v>
+        <v>-17.81309871818411</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-10.91013705002725</v>
+        <v>-10.93062937821189</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-13.34398648152228</v>
+        <v>-13.30812490719919</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.061894876081624</v>
+        <v>-1.307802814297254</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.7644529383659631</v>
+        <v>-1.010360876581593</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.413289219740832</v>
+        <v>-3.525997024756364</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.316370054419764</v>
+        <v>-1.500801008081538</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.63378019701232</v>
+        <v>-11.59279554064303</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-9.909926304287161</v>
+        <v>-9.949432358889297</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.1239499714363</v>
+        <v>-10.12516231307415</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.51164350693908</v>
+        <v>-7.530879392096693</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-8.064052802862868</v>
+        <v>-7.946325031752131</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-15.63099948449002</v>
+        <v>-15.38891139178358</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.106341546016445</v>
+        <v>-4.286000596643213</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>20.08853645392254</v>
+        <v>19.36184379174605</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.790441940874317</v>
+        <v>6.12497837218497</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.920695073481816</v>
+        <v>6.255231504792469</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.06933904481616082</v>
+        <v>-0.5043878669617428</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.905522247738205</v>
+        <v>9.124851305776971</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.369175627240153</v>
+        <v>2.943794556697767</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.12779868007155</v>
+        <v>5.562235211282278</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.840992342276351</v>
+        <v>2.390636246758959</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.369143207037432</v>
+        <v>4.759264814333044</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.280794093276995</v>
+        <v>-1.598591144087081</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.101433869319131</v>
+        <v>1.726851363928645</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.242940264034324</v>
+        <v>7.851855282557104</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.227316882834074</v>
+        <v>4.875770163220558</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-23.92200974878141</v>
+        <v>-23.28425464674061</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.105011933174211</v>
+        <v>-4.190045946779684</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-18.78559492548511</v>
+        <v>-18.70056091187967</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-22.22677036430618</v>
+        <v>-21.97166832348984</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-12.05090586509264</v>
+        <v>-12.22097389230352</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.182035355948386</v>
+        <v>-8.649722430778318</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-5.035476556213879</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-15.87680961485935</v>
+        <v>-15.79177560125392</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12.36638092961308</v>
+        <v>-12.40889793641582</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-13.17774101563493</v>
+        <v>-13.33280141165918</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-17.09880140918349</v>
+        <v>-16.88657461159085</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-20.87194982173254</v>
+        <v>-20.4156612920495</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-17.96057004599719</v>
+        <v>-17.3785594639866</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-21.3682561211283</v>
+        <v>-20.70026670313889</v>
       </c>
     </row>
   </sheetData>
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.3834</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1973953304688862</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.356</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4049~4062</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4049</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2039257648185355</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.3286</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4019~4032</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4019</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.1620891138607661</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.3012</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3971~3983</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3971</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.1710682474005338</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.2738</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3909~3921</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3909</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.1598499498962767</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.2464</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3843~3854</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3843</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2360434058352965</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.219</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3761~3772</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3761</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.1604584686723314</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.1916</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3675~3686</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3675</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.05176713192999216</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.1642</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3577~3587</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3577</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.4164937983253907</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.1368</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3453~3462</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3453</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.500370729222098</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.1094</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3311~3318</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3311</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.3837336788597696</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.08201</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3128~3135</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3128</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.5317158321716988</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.05461</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2884~2891</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2884</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.5045071545233597</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.02721</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2571~2577</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2571</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.9218434424451303</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.0001886</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1617~1623</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1617</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.415188166174246</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.02759</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1293~1299</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1293</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-2.070035702811978</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.05499</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1074~1080</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1074</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-2.58603091280257</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.08239</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>907~913</t>
-        </is>
+      <c r="B23" t="n">
+        <v>907</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-3.643493084722571</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.1098</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>787~793</t>
-        </is>
+      <c r="B24" t="n">
+        <v>787</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-4.321937689692952</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.1372</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>664~670</t>
-        </is>
+      <c r="B25" t="n">
+        <v>664</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-5.627766678418929</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.1646</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>573~579</t>
-        </is>
+      <c r="B26" t="n">
+        <v>573</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-6.552160254579576</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.192</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>481~487</t>
-        </is>
+      <c r="B27" t="n">
+        <v>481</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-5.881528669285949</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.2194</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>406~412</t>
-        </is>
+      <c r="B28" t="n">
+        <v>406</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-6.862370359044924</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.2468</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>338~344</t>
-        </is>
+      <c r="B29" t="n">
+        <v>338</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-5.400415064396022</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.2742</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>278~282</t>
-        </is>
+      <c r="B30" t="n">
+        <v>278</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-4.266487965600049</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.3016</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>226~230</t>
-        </is>
+      <c r="B31" t="n">
+        <v>226</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-5.102133972383889</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.329</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>178~182</t>
-        </is>
+      <c r="B32" t="n">
+        <v>178</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-7.438493265264917</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.3564</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>139~143</t>
-        </is>
+      <c r="B33" t="n">
+        <v>139</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-9.136794963566622</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.3838</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>108~112</t>
-        </is>
+      <c r="B34" t="n">
+        <v>108</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-10.52915260592426</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.4112</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>80~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>80</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.3834</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10.60179977502812</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.356</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>116~116</t>
-        </is>
+      <c r="B7" t="n">
+        <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7.851389265996922</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.3286</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>146~146</t>
-        </is>
+      <c r="B8" t="n">
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5.04080825513249</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.3012</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>194~195</t>
-        </is>
+      <c r="B9" t="n">
+        <v>194</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3.916818090046434</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.2738</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>256~257</t>
-        </is>
+      <c r="B10" t="n">
+        <v>256</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2.759479967727771</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.2464</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>322~324</t>
-        </is>
+      <c r="B11" t="n">
+        <v>322</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.062117235345582</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.219</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>404~406</t>
-        </is>
+      <c r="B12" t="n">
+        <v>404</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.69375379801663</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.1916</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>490~492</t>
-        </is>
+      <c r="B13" t="n">
+        <v>490</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.5553421675949082</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.1642</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>588~591</t>
-        </is>
+      <c r="B14" t="n">
+        <v>588</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.667306180636054</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.1368</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>712~716</t>
-        </is>
+      <c r="B15" t="n">
+        <v>712</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.534494640683882</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.1094</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>854~860</t>
-        </is>
+      <c r="B16" t="n">
+        <v>854</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.576329121650488</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.08201</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1037~1043</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1037</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.677223233001911</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.05461</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1281~1287</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1281</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.197315370543713</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.02721</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1594~1601</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1594</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.535293722263482</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.0001886</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2548~2555</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2548</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.9312192140366022</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.02759</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2872~2879</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2872</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.9626228121276412</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.05499</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3091~3098</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3091</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.928123978046969</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.08239</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3258~3265</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3258</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.044080822209622</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.1098</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3378~3385</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3378</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.036842329716166</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.1372</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3501~3508</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3501</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.098351873632673</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.1646</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3592~3599</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3592</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.07699791207677</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.192</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3684~3691</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3684</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.7983525223801067</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.2194</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3759~3766</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3759</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.7726264700183876</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.2468</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3827~3834</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3827</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.5060400313810476</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.2742</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3887~3896</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3887</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.3299703040200086</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.3016</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3939~3948</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3939</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.3181118317657052</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.329</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3987~3996</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3987</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.359414532642873</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.3564</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4026~4035</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4026</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.3442320639288141</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.3838</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4057~4066</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4057</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.310299997547034</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.4112</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4085~4094</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1445685190670218</v>

--- a/workspaces/btc_daily_14days/williams_r/wr_spread_7_14.xlsx
+++ b/workspaces/btc_daily_14days/williams_r/wr_spread_7_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that WR Spread-7-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that WR Spread-7-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>32</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.6289086908361696</v>
+        <v>0.6413907722427226</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.254450370951311</v>
+        <v>5.267324955263234</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.745236289092759</v>
+        <v>1.758208590181518</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.22720577459035</v>
+        <v>11.24015923530981</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.574531191750111</v>
+        <v>7.58761667035548</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.873207862630551</v>
+        <v>7.886228578224973</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.91037680184665</v>
+        <v>10.92342483225646</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.44665158652776</v>
+        <v>10.45981662017908</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.38839300119364</v>
+        <v>10.4015783679487</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.419776573041403</v>
+        <v>6.433169838649377</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.02853372900260354</v>
+        <v>-0.01508656306442901</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.117569264984724</v>
+        <v>-3.104124109580773</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.538442412484578</v>
+        <v>-3.524889986774539</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.960447582576819</v>
+        <v>2.950017946877246</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.808642438129446</v>
+        <v>-5.796166127887226</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.553940570947539</v>
+        <v>2.566812673240086</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.809160337789649</v>
+        <v>8.822136918167608</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.26585357722258</v>
+        <v>12.27880739193528</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.753963487679002</v>
+        <v>1.767045408127167</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.928920311830979</v>
+        <v>-7.915907684707179</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-8.015290658123703</v>
+        <v>-8.002251020002255</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-8.483664633712458</v>
+        <v>-8.470506805127044</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-8.546585335241296</v>
+        <v>-8.53340597695167</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-9.39791526958841</v>
+        <v>-9.384526073792252</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.943026887175961</v>
+        <v>-2.929580417591083</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.240992569593274</v>
+        <v>-6.227547916166074</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.662652227681512</v>
+        <v>-6.649100054313053</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>48</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.5807471212737383</v>
+        <v>0.593500405355428</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.093448673460429</v>
+        <v>3.106602178715114</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.6155842005617842</v>
+        <v>0.6288382139959623</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7526721945795174</v>
+        <v>0.7659002423606864</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.875123267188407</v>
+        <v>-1.861758867982289</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.635439630750881</v>
+        <v>0.5203147811432913</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.687560503655185</v>
+        <v>-4.674519979102875</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.074930825278088</v>
+        <v>-3.061771457034112</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.024898031430112</v>
+        <v>1.038079989236557</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.905284520210024</v>
+        <v>-1.891893783528808</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.110282561919313</v>
+        <v>-2.096836156556506</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.323217738047006</v>
+        <v>-8.30977351333798</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-10.82823804203424</v>
+        <v>-10.81468621675366</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-8.497885750758883</v>
+        <v>-8.508315386456083</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.8783638110159302</v>
+        <v>-0.8658822578988179</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.773281070001104</v>
+        <v>8.786159190989885</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>18.03426683408769</v>
+        <v>18.04725100323217</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13.34072996611905</v>
+        <v>13.35368601831444</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.587800402972206</v>
+        <v>9.600888378898837</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.055747867603401</v>
+        <v>5.070173851737565</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.192818831690161</v>
+        <v>8.205864466327974</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.118067779924431</v>
+        <v>6.131230112958676</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.447894622656932</v>
+        <v>4.461077238660259</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.599882618660864</v>
+        <v>3.613274377965006</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.396284947151955</v>
+        <v>3.409732115986493</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.404598216242114</v>
+        <v>-1.391153343156013</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.275051711729077</v>
+        <v>-8.26149985760749</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.640358869036767</v>
+        <v>-9.650788504735658</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>66</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.276687189098084</v>
+        <v>4.289376296618293</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11.71425426279252</v>
+        <v>11.72734413513351</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>17.36647309847835</v>
+        <v>17.37966732972252</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.945142347157294</v>
+        <v>9.958306166079844</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.709188550329273</v>
+        <v>7.901686011827096</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>12.03010806947418</v>
+        <v>12.04639494235245</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13.46131285506601</v>
+        <v>13.47436042661107</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>12.99849699272885</v>
+        <v>13.01166157922521</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.401495130163831</v>
+        <v>8.414678598344949</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>13.60888556406471</v>
+        <v>13.62227961969097</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.86601984999885</v>
+        <v>8.879467815533161</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.874139867207639</v>
+        <v>5.887585472264078</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.455561532899765</v>
+        <v>5.469114158283503</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.736962734089857</v>
+        <v>8.726533098392402</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>82</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.702811072541486</v>
+        <v>-3.690330991355644</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-10.17666459801407</v>
+        <v>-10.16379857757247</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.057692513409634</v>
+        <v>-2.044719523760421</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.145070034769653</v>
+        <v>-3.132121756227789</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.465134507907862</v>
+        <v>-2.452509931543631</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.60220134989676</v>
+        <v>-4.590209132930035</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1812700969711756</v>
+        <v>0.1943106396786973</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.502469315463181</v>
+        <v>-1.489311296339523</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3456374219946596</v>
+        <v>-0.3324575222693369</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.241574212397111</v>
+        <v>1.254964491114819</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.399537213295226</v>
+        <v>-1.386091715190574</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.584157914182889</v>
+        <v>-2.57071373498615</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6526454337852172</v>
+        <v>0.6661975996534508</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3169914418148423</v>
+        <v>-0.3274210775129944</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>86</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.805117335277856</v>
+        <v>-4.792640197938901</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.863341932595631</v>
+        <v>2.876215262330732</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.010764089039768</v>
+        <v>-0.997791999399972</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2793566677345325</v>
+        <v>0.2923054996875507</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9026411983283609</v>
+        <v>0.9161599486793648</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.520036719799826</v>
+        <v>3.534191038519182</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.205830240063001</v>
+        <v>-1.192791569714181</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.293084989975803</v>
+        <v>5.306244954520736</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.911409899620246</v>
+        <v>2.924590145389345</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.421522130186602</v>
+        <v>-1.408133294038464</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.859325910187991</v>
+        <v>1.872771582611264</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.056621824678757</v>
+        <v>3.070066451634126</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.799825127279568</v>
+        <v>3.81337735066537</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-0.6110285647506615</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>98</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13.26075619150203</v>
+        <v>13.27339394444669</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.517450212317236</v>
+        <v>4.530475363216496</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.454648639102224</v>
+        <v>-2.989773149034669</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.30714547107528</v>
+        <v>-1.294199152586991</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.228411874929314</v>
+        <v>2.242322247515908</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.561388939359048</v>
+        <v>4.575891553842055</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.533651469283789</v>
+        <v>7.546693478183791</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8.088097468423896</v>
+        <v>8.101257797122805</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.972838459256991</v>
+        <v>4.986018625607457</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.086706879319287</v>
+        <v>2.100095959986817</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.882943589596358</v>
+        <v>1.896388696374558</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.937949409379726</v>
+        <v>2.95139364821744</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.498565168582729</v>
+        <v>1.512117030291904</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.809937378493764</v>
+        <v>4.799507742795612</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>124</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.919208156403229</v>
+        <v>1.93181122884409</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.712873780199807</v>
+        <v>2.725871516919959</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.119654580949522</v>
+        <v>-4.107651814687543</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.379509645509337</v>
+        <v>-2.366441336340529</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2979881214615929</v>
+        <v>0.31139084284316</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.5977829492597877</v>
+        <v>0.6112315386771598</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.970346628195614</v>
+        <v>4.5514345080163</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.505491795158768</v>
+        <v>4.518649270624358</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.472869849553632</v>
+        <v>8.486050432579034</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.404440593683468</v>
+        <v>4.417829474673965</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.201411540475704</v>
+        <v>4.21485648301114</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.819330367768885</v>
+        <v>1.832773933755618</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.3998171759389</v>
+        <v>1.41336876842233</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.262866937413918</v>
+        <v>3.252437301716135</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>142</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.219985333093199</v>
+        <v>-3.573481210448392</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-10.09584687365587</v>
+        <v>-10.46219420715299</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-9.087225533582654</v>
+        <v>-9.076803779728593</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.767302108710439</v>
+        <v>-6.13326250044009</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.304747737821046</v>
+        <v>-6.293315746108959</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.08898192549033</v>
+        <v>-1.076010186119781</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.042539302582341</v>
+        <v>3.056833995292209</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.983193023314293</v>
+        <v>3.99634855453575</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.517597270398767</v>
+        <v>2.530774007948132</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.296892493791198</v>
+        <v>7.310281265376005</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.28052323075741</v>
+        <v>4.293967302164489</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.427993002963049</v>
+        <v>6.44143673712346</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.601905414523777</v>
+        <v>4.615456951630421</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.55727856849105</v>
+        <v>5.546848932792578</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>183</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.145709903433776</v>
+        <v>2.159040838755935</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.097375251374949</v>
+        <v>-1.084775756216715</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.581892311848165</v>
+        <v>-2.569659469275109</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.088265156579297</v>
+        <v>-4.076448629447789</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.261293492874394</v>
+        <v>-6.250022038205252</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.329580909955055</v>
+        <v>-4.317652560924834</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.414920284062326</v>
+        <v>-4.40288205462118</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.610052451178497</v>
+        <v>-1.596902678141952</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.148201365625489</v>
+        <v>2.161375810818406</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.300316228249081</v>
+        <v>1.313701178586513</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5409907688725681</v>
+        <v>-0.5275493981715229</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.329037325455658</v>
+        <v>-4.315596541769729</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.166170736808823</v>
+        <v>0.1797213999963461</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.676847499391819</v>
+        <v>-0.6872771350899711</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>244</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8533134810972314</v>
+        <v>-0.8409027023954749</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4020392457594966</v>
+        <v>0.4151127042466456</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.218279354484274</v>
+        <v>-1.205688331737711</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.773030281565674</v>
+        <v>1.786707023232395</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.443517012299267</v>
+        <v>-2.431194110280586</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.330241254260407</v>
+        <v>-1.317437930204605</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.686419895190909</v>
+        <v>-4.674628013262016</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.745523036526166</v>
+        <v>-4.732380162071287</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.625993999246056</v>
+        <v>-5.612827534439596</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.611360855187009</v>
+        <v>-3.597981087063374</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.5880851032842</v>
+        <v>-2.574646809147822</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3129096540708929</v>
+        <v>0.3263497273699798</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.97483983678093</v>
+        <v>-2.961290339407611</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.955536023981978</v>
+        <v>-3.96596565968013</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>313</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.923517114636041</v>
+        <v>2.937372747084467</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.585199653387392</v>
+        <v>2.599157714306038</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.871080777186087</v>
+        <v>1.884783269245155</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.185580714664241</v>
+        <v>-1.172903602792971</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.143870554378211</v>
+        <v>1.157418087262052</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.426619428952669</v>
+        <v>-1.413905494204997</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.357381173400739</v>
+        <v>1.371247724974737</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.700160281413957</v>
+        <v>1.541744210722861</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.915790919280816</v>
+        <v>2.928956235194221</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.11148209441594</v>
+        <v>1.124858956406484</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.9081973952928593</v>
+        <v>0.921633013138397</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6242029187193836</v>
+        <v>0.6376404804730456</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4341236967969095</v>
+        <v>-0.4205753096305003</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.462475740108303</v>
+        <v>-1.472905375806455</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>954</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.08563964970929305</v>
+        <v>-0.0726002271995938</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.271729479305861</v>
+        <v>-1.259335298833683</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.350713105365315</v>
+        <v>-1.338458215006888</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4905675781458996</v>
+        <v>-0.477697305817756</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8173945484635325</v>
+        <v>-0.8047177206396654</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1042143894198588</v>
+        <v>0.1176172787368657</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3313489884321825</v>
+        <v>0.345208084508684</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2821896679780167</v>
+        <v>0.2963740412847287</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.01289810453155837</v>
+        <v>0.02603549137030114</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6301313294820403</v>
+        <v>0.6434870047623917</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.264719618089636</v>
+        <v>1.278139619566041</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.824370655769478</v>
+        <v>1.837797996805527</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.767918922230493</v>
+        <v>2.781462481421769</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.914588043791333</v>
+        <v>2.904158408093188</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>324</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.198138577259655</v>
+        <v>1.212682001307641</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.136876479865222</v>
+        <v>1.150623817309231</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.43287318927748</v>
+        <v>4.448857563178798</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.79391003768697</v>
+        <v>1.808439506972512</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8901877443427182</v>
+        <v>-0.8779961564478569</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.057022454229653</v>
+        <v>-3.045708633559777</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.759888629639349</v>
+        <v>-3.748410033043299</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.149290345400388</v>
+        <v>-5.138314928633989</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.75297477500439</v>
+        <v>-2.739902430097146</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.370209141755247</v>
+        <v>-6.356915174505581</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.345188990202921</v>
+        <v>-5.331814474271596</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.929128672537509</v>
+        <v>-5.91573298324721</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.660500510848166</v>
+        <v>-6.64697355507149</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.723194392733248</v>
+        <v>-6.733624028431429</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>219</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4604613544021277</v>
+        <v>0.4753397865891245</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2236982426289273</v>
+        <v>-0.2107942916750289</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.469474079876527</v>
+        <v>3.486066688004307</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.234908472392405</v>
+        <v>2.250632379233267</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.706751563196526</v>
+        <v>1.720896414367822</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.905946752154513</v>
+        <v>2.921938488226893</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.086929667393228</v>
+        <v>5.105842826524956</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.257921284400688</v>
+        <v>3.275609526946035</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>6.379921400012577</v>
+        <v>6.392968903874667</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.908783650959762</v>
+        <v>6.922061851493652</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>6.257238096838599</v>
+        <v>6.270597562935563</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.109287783426012</v>
+        <v>3.122667631186019</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.062017073285396</v>
+        <v>4.075536854193125</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.402799180748957</v>
+        <v>3.392369545050705</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>167</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.157191781397692</v>
+        <v>3.176046179887251</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.997419888348233</v>
+        <v>-1.986474022370906</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.362998202763137</v>
+        <v>2.379896784576808</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.896558630965679</v>
+        <v>1.913077608626082</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.157342947874461</v>
+        <v>3.173527196452561</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1247628462554431</v>
+        <v>-0.1108576123264697</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3756347437737588</v>
+        <v>0.3918418503602226</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6839818973219849</v>
+        <v>-0.6687215612234141</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.728373752207169</v>
+        <v>-3.715432394261988</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.359109019309798</v>
+        <v>-6.345934109373815</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.969121564656689</v>
+        <v>-5.955837925371</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.532741998531741</v>
+        <v>-6.519412770793544</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.957659317465129</v>
+        <v>-6.944166287795483</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.312756010239042</v>
+        <v>-7.323185645937023</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>120</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8059727828748535</v>
+        <v>0.8241487775918586</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.71609088921246</v>
+        <v>1.731039117279543</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.136648279989409</v>
+        <v>2.154678369224726</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.265243974636917</v>
+        <v>2.283522314513107</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.398282184332501</v>
+        <v>3.415893393168311</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3784955608930147</v>
+        <v>0.3933547329519129</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.374382705226985</v>
+        <v>-1.359253861465149</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.470690143266552</v>
+        <v>1.489446589699519</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2481671502151528</v>
+        <v>-0.2352902070740583</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.893267532634006</v>
+        <v>3.906418392268009</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4526152139851902</v>
+        <v>-0.4393725519875318</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>8.731761709290922</v>
+        <v>8.745090404102434</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.163138349555929</v>
+        <v>4.176623585912715</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.752114249242062</v>
+        <v>2.741684613543867</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>123</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.727415550258705</v>
+        <v>2.750554335777601</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.002153773065267</v>
+        <v>6.024302902604084</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>9.618983104436836</v>
+        <v>9.650119991223612</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.55270512885995</v>
+        <v>10.58540389967188</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>11.64719523452537</v>
+        <v>11.67887649055131</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.713822341648317</v>
+        <v>8.741899407971516</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.38923952000706</v>
+        <v>5.415309375010374</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.700275564408862</v>
+        <v>1.721418180488946</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.02530781557018713</v>
+        <v>0.03808458184109043</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.002161542182498977</v>
+        <v>0.01520310411478931</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.473134717114718</v>
+        <v>5.486343515512971</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.142319996447071</v>
+        <v>7.155609774526219</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.679466000814479</v>
+        <v>2.692925299757718</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.122032948429009</v>
+        <v>2.111603312730857</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>91</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1928654000431607</v>
+        <v>0.215545860885392</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.255753277950525</v>
+        <v>6.281795625599258</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.567410587291448</v>
+        <v>2.593012038008247</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.605510184778936</v>
+        <v>1.629959052513065</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>7.618463509636022</v>
+        <v>7.650049381592829</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>7.911265434978297</v>
+        <v>7.943556734250123</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.54697777076354</v>
+        <v>4.576434203081362</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.175041248684309</v>
+        <v>5.205221473029965</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.943706338051776</v>
+        <v>2.956394166014185</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.397276661285453</v>
+        <v>5.410262829410726</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.930971725678894</v>
+        <v>1.944080221391374</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.976906038690892</v>
+        <v>1.990122484783818</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.959324914609276</v>
+        <v>5.97276196360864</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.222810219938104</v>
+        <v>6.212380584239881</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>92</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-10.05839712986473</v>
+        <v>-10.05316431394233</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.231926952327321</v>
+        <v>-6.226850146805468</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.662969335126959</v>
+        <v>-6.651766261729733</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-7.610536789411938</v>
+        <v>-7.600884360841576</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.904856927276349</v>
+        <v>-4.892278088727942</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.613798579478946</v>
+        <v>-4.600223717358048</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-10.0833795046014</v>
+        <v>-10.07810385128198</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-9.468486589878268</v>
+        <v>-9.462282813525022</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-10.62019241600229</v>
+        <v>-10.60792787101322</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-6.071504927759477</v>
+        <v>-6.058819890381038</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.191726496604446</v>
+        <v>-5.178815801987547</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-7.321073779137677</v>
+        <v>-7.308010006900886</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.487642018434201</v>
+        <v>-4.474284180980071</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.066726330468086</v>
+        <v>-2.077155966166167</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>75</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5719056553907294</v>
+        <v>-0.5463054765182846</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.5280828350056055</v>
+        <v>0.546587960996149</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.08237782131784854</v>
+        <v>0.1094529869984555</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.104275274685172</v>
+        <v>-1.079965948810937</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-6.874436952135262</v>
+        <v>-6.866928109443684</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.644218554620089</v>
+        <v>-2.62557369664237</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.679670957723964</v>
+        <v>-6.669216294101531</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.059527759746828</v>
+        <v>2.091255714544175</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.32519308366949</v>
+        <v>3.337457758230173</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.831807402367573</v>
+        <v>3.844435098125686</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.655825512098353</v>
+        <v>3.668673302864008</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.591601650021296</v>
+        <v>-1.578637465054733</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.980446413691539</v>
+        <v>5.993783575423102</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.918780915908727</v>
+        <v>4.908351280210574</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-14.12914814715267</v>
+        <v>-14.13812520004543</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.181267361965801</v>
+        <v>-1.165452235826464</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.093043350779823</v>
+        <v>-3.069411061645006</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.962790218172323</v>
+        <v>-2.939185918056644</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.895348338401696</v>
+        <v>-4.884354264665724</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.733430287368662</v>
+        <v>-1.709720728834832</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.818164004640941</v>
+        <v>-1.794431088101</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.637096570011714</v>
+        <v>-6.623251488359124</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.162613917072903</v>
+        <v>-8.151086473166075</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.090764932417166</v>
+        <v>-6.078687092128845</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.283779835196135</v>
+        <v>-6.271363487628655</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.774872656633768</v>
+        <v>-4.762150718768297</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-13.98936420857586</v>
+        <v>-13.97626556955453</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-7.885140652718718</v>
+        <v>-7.89557028841687</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-10.65427728881735</v>
+        <v>-10.55562611021677</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.780612570922287</v>
+        <v>-5.7116406845551</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.731641594193839</v>
+        <v>-7.713310131460865</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.613741562054301</v>
+        <v>0.4973707730855068</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.29079398489521</v>
+        <v>3.183794138714823</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.988642761909297</v>
+        <v>1.869673561178764</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.546935049365153</v>
+        <v>3.401054354104204</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2008712533691934</v>
+        <v>-0.2976220259381464</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5332875497340979</v>
+        <v>-0.3563059099507839</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.005350424690732</v>
+        <v>2.801377439989793</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.174921262060842</v>
+        <v>1.023980596127615</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.535164219174966</v>
+        <v>4.356389821003319</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.76935456888311</v>
+        <v>10.51440570543603</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>4.230755651795278</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>52</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6346418591934224</v>
+        <v>-0.6221195695177997</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.386318506352346</v>
+        <v>5.399228315928397</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7699534593348645</v>
+        <v>-0.7569463279172624</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.560168079757553</v>
+        <v>-2.547188937359088</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.638145447455422</v>
+        <v>2.651256251830361</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-10.33500726840229</v>
+        <v>-10.32196437210793</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-12.31554022189935</v>
+        <v>-12.30247396759887</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-8.997292277432635</v>
+        <v>-8.984111268137397</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.193328573396947</v>
+        <v>-7.180129834442184</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.025146634170554</v>
+        <v>-8.023881501570742</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.300332120662802</v>
+        <v>-6.2999105807219</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-4.333361309382788</v>
+        <v>-4.333757519016075</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.818119903546993</v>
+        <v>-2.817559877012577</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.568398571270755</v>
+        <v>-2.578828206968907</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>48</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.56186507204994</v>
+        <v>3.574387361725563</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.01080903462352722</v>
+        <v>0.002100774952523921</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.517200105570822</v>
+        <v>1.530207236988424</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-4.503406771377335</v>
+        <v>-4.490427628978871</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.147254670024424</v>
+        <v>1.160365474399363</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.444696607740084</v>
+        <v>1.45773950403445</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-6.790220259715284</v>
+        <v>-6.777154005414808</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-9.304505107772179</v>
+        <v>-9.291324098476942</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-11.45082909014818</v>
+        <v>-11.43763035119341</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-8.198448926748569</v>
+        <v>-8.202901910702082</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.312515356530305</v>
+        <v>-6.319228579799599</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.252632827137333</v>
+        <v>-6.2500600274238</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-14.99760708303422</v>
+        <v>-14.93626557494785</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.331219084091266</v>
+        <v>-4.341648719789418</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.385571827728086</v>
+        <v>-1.373049538052463</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-17.81309871818411</v>
+        <v>-17.80018890860806</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-10.93062937821189</v>
+        <v>-10.91762224679429</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-13.30812490719919</v>
+        <v>-13.29514576480072</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.307802814297254</v>
+        <v>-1.294692009922315</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.010360876581593</v>
+        <v>-0.9973179802872281</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.525997024756364</v>
+        <v>-3.512930770455888</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.500801008081538</v>
+        <v>-1.4876199987863</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.59279554064303</v>
+        <v>-11.57959680168827</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-9.949432358889297</v>
+        <v>-9.952505428700306</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.12516231307415</v>
+        <v>-10.11738390268633</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.530879392096693</v>
+        <v>-7.52595389010375</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-7.946325031752131</v>
+        <v>-7.905654572811358</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-15.38891139178358</v>
+        <v>-15.39934102748173</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.286000596643213</v>
+        <v>-4.27347830696759</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>19.36184379174605</v>
+        <v>19.3747536013221</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.12497837218497</v>
+        <v>6.137985503602572</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.255231504792469</v>
+        <v>6.268210647190934</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5043878669617428</v>
+        <v>-0.4912770625868035</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.124851305776971</v>
+        <v>9.137894202071337</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.943794556697767</v>
+        <v>2.956860810998243</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.562235211282278</v>
+        <v>5.575416220577516</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.390636246758959</v>
+        <v>2.403834985713722</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.759264814333044</v>
+        <v>4.61456521777486</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.598591144087081</v>
+        <v>-1.671209967947377</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.726851363928645</v>
+        <v>1.642189540222226</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.851855282557104</v>
+        <v>7.765001232937905</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.875770163220558</v>
+        <v>4.865340527522406</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-23.28425464674061</v>
+        <v>-23.27173235706498</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.190045946779684</v>
+        <v>-4.177136137203632</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-18.70056091187967</v>
+        <v>-18.68755378046207</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-21.97166832348984</v>
+        <v>-21.95868918109138</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-12.22097389230352</v>
+        <v>-12.20786308792858</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.649722430778318</v>
+        <v>-8.636679534483953</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-5.035476556213879</v>
+        <v>-5.022410301913403</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-15.79177560125392</v>
+        <v>-15.77859459195869</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12.40889793641582</v>
+        <v>-12.39569919746106</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-13.33280141165918</v>
+        <v>-13.37316901419904</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-16.88657461159085</v>
+        <v>-16.83618750134455</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-20.4156612920495</v>
+        <v>-20.30088677401433</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-17.3785594639866</v>
+        <v>-17.22706512984963</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-20.70026670313889</v>
+        <v>-20.71069633883704</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that WR Spread-7-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that WR Spread-7-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1973953304688862</v>
+        <v>-0.1976437472620631</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01177282128460178</v>
+        <v>0.01146407083269452</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05217780497121538</v>
+        <v>-0.05247331289756119</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1774984433647475</v>
+        <v>-0.1777627342663308</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2625719496193497</v>
+        <v>-0.2628186316224728</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3186038498169665</v>
+        <v>-0.3188352818685019</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2432857072715677</v>
+        <v>-0.2435361697220131</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2322572012831827</v>
+        <v>-0.2325131456815015</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2063921176418617</v>
+        <v>-0.2066548740795966</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2352156792501745</v>
+        <v>-0.2354763453547051</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2059243333198353</v>
+        <v>-0.2061934724034415</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1822998147295394</v>
+        <v>-0.1825746854913106</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1723580221163701</v>
+        <v>-0.1726378600967706</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2273434000269035</v>
+        <v>-0.227039867919423</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4049</v>
+        <v>4050</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2039257648185355</v>
+        <v>-0.2042731558112436</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.02966103438082968</v>
+        <v>-0.0300637188714532</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.06638310282501436</v>
+        <v>-0.06677993534164273</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2676319417531232</v>
+        <v>-0.26797841402594</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.324510033226133</v>
+        <v>-0.3248467624035385</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3833452612267649</v>
+        <v>-0.3836654160717003</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3314351763483288</v>
+        <v>-0.3317689480092554</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3166546034096172</v>
+        <v>-0.3169957512389203</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2901246747677533</v>
+        <v>-0.2904730132758715</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2878113206612127</v>
+        <v>-0.2881668831048572</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2073262842554158</v>
+        <v>-0.2077034529216704</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1591018343867034</v>
+        <v>-0.1594908381898748</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1457552311823633</v>
+        <v>-0.1461509297131443</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2525371050017853</v>
+        <v>-0.2521425469499121</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4019</v>
+        <v>4020</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.1620891138607661</v>
+        <v>-0.1625426112435022</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.04894644074059329</v>
+        <v>-0.04944339343944648</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1326349822025819</v>
+        <v>-0.1331151357409581</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3611886885979274</v>
+        <v>-0.3616111439211807</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3400248890676707</v>
+        <v>-0.3404578980045088</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3270209886420119</v>
+        <v>-0.3274546528729303</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2740787034811305</v>
+        <v>-0.2745265444869176</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2556916024369684</v>
+        <v>-0.2561486538218389</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2284939656823539</v>
+        <v>-0.2289585881738176</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.219808554185029</v>
+        <v>-0.2202836055624218</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1869055283241892</v>
+        <v>-0.1873909382599592</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1137032969255927</v>
+        <v>-0.1142068301452781</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.0971095705964089</v>
+        <v>-0.0976214586340447</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2065404741551404</v>
+        <v>-0.2060765804859415</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3971</v>
+        <v>3972</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1710682474005338</v>
+        <v>-0.1716790827431893</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.08693056702657032</v>
+        <v>-0.08758291697001397</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1416791828504458</v>
+        <v>-0.142323031206061</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3746526327914594</v>
+        <v>-0.3752366591632494</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3214691796368498</v>
+        <v>-0.3220735962525154</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3507424970104012</v>
+        <v>-0.3376996007160358</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2207301448288135</v>
+        <v>-0.2213544183888416</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2216136667289987</v>
+        <v>-0.2222438465322654</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2436445111019907</v>
+        <v>-0.2442702326138217</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1994351353058477</v>
+        <v>-0.2000828783362394</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1636564480893341</v>
+        <v>-0.1643160715735945</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01446967990877113</v>
+        <v>-0.01516674938162055</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.03260439732831344</v>
+        <v>0.03188989795954456</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1063177158381023</v>
+        <v>-0.1057474106252698</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3909</v>
+        <v>3910</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1598499498962767</v>
+        <v>-0.1606712574593914</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2274609127660696</v>
+        <v>-0.2282918711115727</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4299648449251947</v>
+        <v>-0.4307510593736268</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5921900390673542</v>
+        <v>-0.5929331312869337</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4786384592791464</v>
+        <v>-0.4794197963699958</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4364939430595314</v>
+        <v>-0.423451046765166</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3541760482681084</v>
+        <v>-0.3549829531337068</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.322166301595324</v>
+        <v>-0.3229894694193334</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.3180562343798243</v>
+        <v>-0.3188818804959155</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2596954834117469</v>
+        <v>-0.2605504358530339</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2201200875124556</v>
+        <v>-0.2209889584351572</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.007578918006984736</v>
+        <v>0.006651963870055511</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1643707515778772</v>
+        <v>0.1633963339813249</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.04490012798342491</v>
+        <v>0.04560618217136181</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3843</v>
+        <v>3844</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2360434058352965</v>
+        <v>-0.2370768606251374</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.432548917342416</v>
+        <v>-0.4335655382323225</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7356023427822436</v>
+        <v>-0.7365490858253239</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7731590574100125</v>
+        <v>-0.7740938476309083</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.6364309606151295</v>
+        <v>-0.6233201562401902</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6505963976073375</v>
+        <v>-0.6375535013129721</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5914443978960122</v>
+        <v>-0.5924274544508705</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5509364752683368</v>
+        <v>-0.5519402938757736</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4678065310386614</v>
+        <v>-0.4688337513605134</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4978756419164085</v>
+        <v>-0.4989132828004514</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3761662066578424</v>
+        <v>-0.3772402974262974</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09317388517990821</v>
+        <v>-0.09432140021788626</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.07349940326477622</v>
+        <v>0.07229920172223814</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1043780744633764</v>
+        <v>-0.1034419906877915</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3761</v>
+        <v>3762</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1604584686723314</v>
+        <v>-0.1618065685677479</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2201007690267929</v>
+        <v>-0.2214764608198081</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.7067771914949645</v>
+        <v>-0.7080350039777272</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7214449653750492</v>
+        <v>-0.7226961101229463</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5965602637584411</v>
+        <v>-0.5834494593835018</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5644406927182928</v>
+        <v>-0.5513977964239274</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.6082916695203409</v>
+        <v>-0.6095759190225394</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5301904787525302</v>
+        <v>-0.5315084963739096</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4704701489439103</v>
+        <v>-0.4718063326432045</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5358003662061535</v>
+        <v>-0.5371424102489044</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3538539432852659</v>
+        <v>-0.3552504472783227</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.0388636776876865</v>
+        <v>-0.04034368319209847</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.06087244912951917</v>
+        <v>0.05935404791300414</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09974252643816328</v>
+        <v>-0.09855993722695189</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3675</v>
+        <v>3676</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.05176713192999216</v>
+        <v>-0.05346824100357139</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2922575234048921</v>
+        <v>-0.2939469418293257</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.6996634845048035</v>
+        <v>-0.7012561406463007</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7448650852246885</v>
+        <v>-0.7464420672621443</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6316436177011511</v>
+        <v>-0.6185328133262118</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6600230212833367</v>
+        <v>-0.6469801249889713</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5943084539919994</v>
+        <v>-0.5959315920477053</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6664630475445392</v>
+        <v>-0.6680827065961381</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5496107432776469</v>
+        <v>-0.5512650097680023</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5150732718653828</v>
+        <v>-0.5167655832614457</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4056453629856023</v>
+        <v>-0.4073750105455858</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1113022499879719</v>
+        <v>-0.1131117113735556</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.02662413054963508</v>
+        <v>-0.02847130683038301</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.08802180517970726</v>
+        <v>-0.08657073647422209</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4164937983253907</v>
+        <v>-0.4184857072344599</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4240303380822041</v>
+        <v>-0.4260859540972035</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6515816994473411</v>
+        <v>-0.638574568029739</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7294601431465892</v>
+        <v>-0.7314392180833167</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7100013024307543</v>
+        <v>-0.696890498055815</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.803075403766691</v>
+        <v>-0.7900325074723256</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8169922875064017</v>
+        <v>-0.8189548611596891</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.9063140205847731</v>
+        <v>-0.9082714627069421</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7009107214292811</v>
+        <v>-0.70292901096051</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5863549198430462</v>
+        <v>-0.5884403823777973</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4683464301796292</v>
+        <v>-0.4704741841839919</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1948433913405054</v>
+        <v>-0.1970472969632482</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.06841013874504398</v>
+        <v>-0.07066740997125009</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2222124677460968</v>
+        <v>-0.2203984868846334</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.500370729222098</v>
+        <v>-0.5028623198788509</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5366790813972884</v>
+        <v>-0.5392425048806757</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.527040420181109</v>
+        <v>-0.5140332887635068</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6702055418454052</v>
+        <v>-0.6727419793271281</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7461990112528341</v>
+        <v>-0.7330882068778948</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8533813509938213</v>
+        <v>-0.8403384546994559</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.024820270578239</v>
+        <v>-1.011754016277763</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.100656308784075</v>
+        <v>-1.103100116711893</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.030348540949085</v>
+        <v>-1.032817097526497</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.765578390354861</v>
+        <v>-0.768167499423086</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6360411849903045</v>
+        <v>-0.6386794542280541</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2671739868022982</v>
+        <v>-0.2699187018877254</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1211353594287345</v>
+        <v>-0.1239449102957408</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3473644649195293</v>
+        <v>-0.3450746993300555</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3837336788597696</v>
+        <v>-0.3712113891841469</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.126711752342402</v>
+        <v>-0.1138019427663508</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1599168061361027</v>
+        <v>-0.1469096747185006</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4516046017986426</v>
+        <v>-0.4386254594001784</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5078076131336289</v>
+        <v>-0.4946968087586896</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8432770678230241</v>
+        <v>-0.8302341715286587</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.199258524697477</v>
+        <v>-1.186192270397001</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.318689110100287</v>
+        <v>-1.321735899114415</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.182510517757116</v>
+        <v>-1.185603914246727</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.111356362432403</v>
+        <v>-1.114526111923531</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8468995803500619</v>
+        <v>-0.8501637052569606</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5543119247505501</v>
+        <v>-0.5576640135844571</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3236940395559671</v>
+        <v>-0.3271439031681851</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-0.5976873671324157</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5317158321716988</v>
+        <v>-0.5191935424960761</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.06992421387598569</v>
+        <v>-0.05701440429993454</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.01822194758581475</v>
+        <v>-0.005214816168212622</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2388460079607739</v>
+        <v>-0.2258668655623097</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1712066169723272</v>
+        <v>-0.1580958125973879</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.6393149184911309</v>
+        <v>-0.6262720221967655</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.011129975476322</v>
+        <v>-0.9980637211758463</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.301643236885027</v>
+        <v>-1.305642731788737</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.381352488771149</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.252448460928157</v>
+        <v>-1.256541322586159</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8647964193847102</v>
+        <v>-0.8690318478573502</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3334760077655687</v>
+        <v>-0.3378808072380579</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3523530082499491</v>
+        <v>-0.3567879908892166</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5961380951739628</v>
+        <v>-0.5924476970984642</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5045071545233597</v>
+        <v>-0.491984864847737</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1098545481863411</v>
+        <v>-0.09694473861028996</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.08330856811571863</v>
+        <v>0.09631569953332075</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4090602294047585</v>
+        <v>-0.3960810870062943</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.02104155794437901</v>
+        <v>0.03415236231931829</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5808592923026055</v>
+        <v>-0.5678163960082401</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7001831168042187</v>
+        <v>-0.6871168625037427</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.010274765625518</v>
+        <v>-1.015825077373151</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.017916310120405</v>
+        <v>-1.023473836728485</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.052873348515135</v>
+        <v>-1.058513141465724</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7189980702614491</v>
+        <v>-0.724778797405051</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3881632829001376</v>
+        <v>-0.394058363717896</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1304782557667394</v>
+        <v>-0.136511189142773</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.3119171885757837</v>
+        <v>-0.3071310999165178</v>
       </c>
     </row>
     <row r="19">
@@ -2890,101 +2890,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9218434424451303</v>
+        <v>-0.9093211527695075</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4379572183895988</v>
+        <v>-0.4250474088135476</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1343393126462544</v>
+        <v>-0.1213321812286523</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3145246744120627</v>
+        <v>-0.3015455320135985</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1156544653476388</v>
+        <v>-0.1025436609726995</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.477894328175239</v>
+        <v>-0.4648514318808736</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9506761634141512</v>
+        <v>-0.9376099091136751</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.340249938602319</v>
+        <v>-1.327068929307082</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.496815712221753</v>
+        <v>-1.504465521219849</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.316367418385774</v>
+        <v>-1.324218999410512</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9170969347960636</v>
+        <v>-0.9251391771484876</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5114112879981221</v>
+        <v>-0.519611139080169</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.0935116968237466</v>
+        <v>-0.101941955195386</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1718452995716291</v>
+        <v>-0.1652619909143596</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.0001886</t>
+          <t>X &gt; 0.0001913</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.415188166174246</v>
+        <v>-1.402665876498624</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.05395294667788875</v>
+        <v>0.06686275625393989</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5832986578262194</v>
+        <v>0.5963057892438215</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2106626273112013</v>
+        <v>-0.1976834849127371</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2983591643941992</v>
+        <v>0.3114699687691385</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8213276717656655</v>
+        <v>-0.8082847754713001</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.707047217750208</v>
+        <v>-1.693980963449732</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.297459205564365</v>
+        <v>-2.284278196269128</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.387518854573422</v>
+        <v>-2.406874647308236</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.464765566478476</v>
+        <v>-2.484411538335699</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.204328222027343</v>
+        <v>-2.224229394741599</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.889479299348942</v>
+        <v>-1.90957919571489</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.781702674299162</v>
+        <v>-1.802045683583998</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.992783709941605</v>
+        <v>-1.975043857819919</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.070035702811978</v>
+        <v>-2.057513413136355</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2174060825198794</v>
+        <v>-0.2044962729438282</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3813279068993864</v>
+        <v>-0.3683207754817843</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7129685387260665</v>
+        <v>-0.6999893963276023</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.5961853039384906</v>
+        <v>0.6092961083134298</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2611071694313054</v>
+        <v>-0.24806427313694</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.192646121499571</v>
+        <v>-1.179579867199095</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.582847226208713</v>
+        <v>-1.569666216913475</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.295942893073324</v>
+        <v>-2.323489020087521</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.486139334158551</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.417291184990304</v>
+        <v>-1.446132357826826</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8772237719606224</v>
+        <v>-0.9064927759618087</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.5591732860223786</v>
+        <v>-0.5889416415732285</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8074371815390649</v>
+        <v>-0.7835601056729899</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.58603091280257</v>
+        <v>-2.573508623126948</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2161230442853466</v>
+        <v>-0.2032132347092954</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.314071951607765</v>
+        <v>-1.301092809209301</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3697290555422867</v>
+        <v>0.382839859917226</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9069030808161216</v>
+        <v>-0.8938601845217562</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.473118279569881</v>
+        <v>-2.460052025269405</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.569931307981022</v>
+        <v>-2.556750298685785</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.065043712613189</v>
+        <v>-4.099213936690042</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.197953238945246</v>
+        <v>-3.233552463222757</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.982209167039208</v>
+        <v>-3.018191755637957</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.690115793031083</v>
+        <v>-1.727317082162159</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.501483052026479</v>
+        <v>-1.539193539780513</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.665949065469299</v>
+        <v>-1.634284378704145</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.643493084722571</v>
+        <v>-3.630970795046949</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1118555367052849</v>
+        <v>0.1247653462813361</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.816419522574762</v>
+        <v>-1.80341239115716</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.905224440350615</v>
+        <v>-1.892245297952151</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1435361263975921</v>
+        <v>-0.1304253220226528</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.050913465790366</v>
+        <v>-1.037870569496</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.997640611321138</v>
+        <v>-2.984574357020662</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.917178884144256</v>
+        <v>-2.903997874849019</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.127032558685741</v>
+        <v>-4.169799308480229</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.615910223155957</v>
+        <v>-2.661121037113467</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.432248449947572</v>
+        <v>-2.477897801513045</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.7984745843005356</v>
+        <v>-0.8459514654204909</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4968728686436137</v>
+        <v>-0.5451071422931761</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.6262392972481976</v>
+        <v>-0.5879776478364178</v>
       </c>
     </row>
     <row r="24">
@@ -3150,49 +3150,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.321937689692952</v>
+        <v>-4.309415400017329</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1327546822284589</v>
+        <v>-0.1198448726524077</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.419174460703985</v>
+        <v>-2.406167329286383</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.541128137680353</v>
+        <v>-2.528148995281889</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6835846617058579</v>
+        <v>-0.6704738573309186</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.268866557533698</v>
+        <v>-1.255823661239333</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.245151346684928</v>
+        <v>-3.232085092384452</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.586231340674495</v>
+        <v>-3.573050331379257</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.718473281705407</v>
+        <v>-4.768963131029395</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.608415090620753</v>
+        <v>-3.661253945141105</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.734098498633067</v>
+        <v>-2.788333118699676</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.251623701493635</v>
+        <v>-2.306516217124489</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.207420957822713</v>
+        <v>-1.264152430852448</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.141363090868055</v>
+        <v>-1.095032814544076</v>
       </c>
     </row>
     <row r="25">
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.627766678418929</v>
+        <v>-5.615244388743307</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.269191037651844</v>
+        <v>-1.256281228075792</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.649134371114108</v>
+        <v>-4.636127239696506</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.96664243253646</v>
+        <v>-4.953663290137996</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.967750214772799</v>
+        <v>-2.95463941039786</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.11806947108699</v>
+        <v>-3.105026574792625</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.844594233135396</v>
+        <v>-4.83152797883492</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.56550897520048</v>
+        <v>-4.552327965905242</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.597215864483864</v>
+        <v>-5.658086241831001</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-4.277241786155095</v>
+        <v>-4.341260286582425</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.254414290104414</v>
+        <v>-4.318837217960059</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.99176688650374</v>
+        <v>-4.05665380655762</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.927431644437725</v>
+        <v>-1.99606304869463</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.745877718629416</v>
+        <v>-1.68813994785959</v>
       </c>
     </row>
     <row r="26">
@@ -3254,49 +3254,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-6.552160254579576</v>
+        <v>-6.539637964903953</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.46425200225886</v>
+        <v>-2.451342192682809</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-5.795217427335587</v>
+        <v>-5.782210295917984</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-6.010387438078695</v>
+        <v>-5.997408295680231</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.648981364722538</v>
+        <v>-4.635870560347598</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.869674142032785</v>
+        <v>-4.85663124573842</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-6.336100432707482</v>
+        <v>-6.323034178407006</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-6.112437544787774</v>
+        <v>-6.099256535492536</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.953627592984283</v>
+        <v>-7.023796550391822</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.813683633828902</v>
+        <v>-5.887233463508167</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.236735629434754</v>
+        <v>-5.31173876322309</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.939671312669027</v>
+        <v>-5.015289072258099</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.179953192209595</v>
+        <v>-3.259413355523201</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.011411056168058</v>
+        <v>-2.94066149563146</v>
       </c>
     </row>
     <row r="27">
@@ -3306,49 +3306,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-5.881528669285949</v>
+        <v>-5.869006379610326</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.743615629272789</v>
+        <v>-1.730705819696738</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.629244089462809</v>
+        <v>-5.616236958045207</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-5.704329765890222</v>
+        <v>-5.691350623491758</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.600040508683136</v>
+        <v>-4.586929704308197</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.918614998072194</v>
+        <v>-4.905572101777828</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.61936514244919</v>
+        <v>-5.606298888148714</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.470532114125973</v>
+        <v>-5.457351104830735</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.252330371118056</v>
+        <v>-6.339688497493135</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.764370621268377</v>
+        <v>-5.854482527258575</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-5.24534444486175</v>
+        <v>-5.337109950844813</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-4.484184770225966</v>
+        <v>-4.577674288052414</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.929833915675992</v>
+        <v>-3.027529297552178</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.192099194971377</v>
+        <v>-3.105479978433955</v>
       </c>
     </row>
     <row r="28">
@@ -3358,49 +3358,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-6.862370359044924</v>
+        <v>-6.849848069369301</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.163264360358703</v>
+        <v>-2.150354550782652</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.6843466591883</v>
+        <v>-6.671339527770698</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-6.5540935265808</v>
+        <v>-6.541114384182336</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.179893382429668</v>
+        <v>-4.166782578054729</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.338762124325655</v>
+        <v>-5.325719228031289</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.423495841597934</v>
+        <v>-5.410429587297457</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.861553026787199</v>
+        <v>-6.848372017491961</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.021577314736447</v>
+        <v>-8.12294640702445</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.537063605930186</v>
+        <v>-7.641752359946089</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.889649239866699</v>
+        <v>-6.996652319464374</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.018528942677563</v>
+        <v>-5.130322351258378</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.575821661248803</v>
+        <v>-4.689933389623789</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.690414486390118</v>
+        <v>-4.582230210370909</v>
       </c>
     </row>
     <row r="29">
@@ -3410,49 +3410,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.400415064396022</v>
+        <v>-5.387892774720399</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.360825886662603</v>
+        <v>-2.347916077086552</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.406857383956869</v>
+        <v>-7.393850252539266</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.276604251349369</v>
+        <v>-7.263625108950905</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.035955698979677</v>
+        <v>-4.022844894604738</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.064095156612858</v>
+        <v>-6.051052260318492</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-6.148828873885137</v>
+        <v>-6.135762619584661</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-6.906709947085233</v>
+        <v>-6.893528937789995</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7.993203087047455</v>
+        <v>-8.117301791987195</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-7.82803493669612</v>
+        <v>-7.955287575909431</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.011540126013443</v>
+        <v>-7.142137984847345</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.067548550520698</v>
+        <v>-5.204173888159048</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.681972864745141</v>
+        <v>-2.827188291584584</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.047688512099157</v>
+        <v>-3.917607421854321</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>278</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.266487965600049</v>
+        <v>-4.253965675924427</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.622742429628133</v>
+        <v>-1.609832620052082</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.336760072394931</v>
+        <v>-7.323752940977329</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-8.979556585177505</v>
+        <v>-8.966577442779041</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-5.617268580391524</v>
+        <v>-5.604157776016585</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.802096146221956</v>
+        <v>-7.789053249927591</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-8.241439792572251</v>
+        <v>-8.228373538271775</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-8.354013262275735</v>
+        <v>-8.340832252980498</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-9.833452864770095</v>
+        <v>-9.820254125815332</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-10.1661756621753</v>
+        <v>-10.31556299306718</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.778402296101419</v>
+        <v>-8.933984148298677</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.140076486426238</v>
+        <v>-7.301995421464454</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.585137059053402</v>
+        <v>-5.754660355679036</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.695127956992948</v>
+        <v>-5.7055575926911</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>226</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-5.102133972383889</v>
+        <v>-5.089611682708266</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.235446715782935</v>
+        <v>-3.222536906206884</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.847706726727345</v>
+        <v>-8.834699595309743</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-10.45658402890245</v>
+        <v>-10.44360488650398</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.516744374409406</v>
+        <v>-7.503633570034467</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-7.219302436693745</v>
+        <v>-7.20625954039938</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-7.304036153966024</v>
+        <v>-7.290969899665548</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-8.206002161443173</v>
+        <v>-8.192821152147935</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-10.44091509110373</v>
+        <v>-10.42771635214897</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-10.65880181021178</v>
+        <v>-10.84285253978318</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-9.348577734697912</v>
+        <v>-9.540054172696877</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.785869359020303</v>
+        <v>-7.984952814948159</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.221795873594694</v>
+        <v>-6.430453386168665</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>178</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.438493265264917</v>
+        <v>-7.425970975589294</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>-11.62973065121037</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-12.06193519947102</v>
+        <v>-12.04895605707255</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-9.853103667290434</v>
+        <v>-9.839992862915494</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-9.555661729574773</v>
+        <v>-9.542618833280407</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-7.442593249044862</v>
+        <v>-7.429526994744386</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-7.909776647826362</v>
+        <v>-7.896595638531124</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-10.16857873181085</v>
+        <v>-10.15537999285609</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-11.32226775631423</v>
+        <v>-11.5547493386365</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.1672911849903</v>
+        <v>-10.40859141123098</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-8.19932640132582</v>
+        <v>-8.452789072258099</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.855284985655949</v>
+        <v>-4.136751222902362</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-6.976350170233594</v>
+        <v>-6.986779805931747</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>139</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.136794963566622</v>
+        <v>-9.124272673890999</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.84253798242817</v>
+        <v>-11.82953085101057</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.71228484982067</v>
+        <v>-11.69930570742221</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-12.25070606489284</v>
+        <v>-12.2375952605179</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-11.95326412717718</v>
+        <v>-11.94022123088281</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.541494347945957</v>
+        <v>-8.528428093645481</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.707978446028157</v>
+        <v>-9.694797436732919</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.768978332210459</v>
+        <v>-9.755779593255696</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-11.70745178868525</v>
+        <v>-12.00429978818695</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-10.17911151595958</v>
+        <v>-10.49029711506726</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-8.386876281613127</v>
+        <v>-8.712836353581977</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.707439217326794</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.615991266345468</v>
+        <v>-4.62642090204362</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>108</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.52915260592426</v>
+        <v>-10.51663031624864</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.890726218888517</v>
+        <v>-5.877816409312466</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-16.99988063977082</v>
+        <v>-16.98687350835322</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-16.86962750716332</v>
+        <v>-16.85664836476486</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-15.62233443652121</v>
+        <v>-15.60922363214627</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-18.00346392737698</v>
+        <v>-17.99042103108261</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-11.83819764464926</v>
+        <v>-11.82513139034878</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-14.09109532914504</v>
+        <v>-14.0779143198498</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.2592380724702</v>
+        <v>-13.24603933351543</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-16.4340093321442</v>
+        <v>-16.77452955841672</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-12.64203865973779</v>
+        <v>-13.02170175914796</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-11.28989069838902</v>
+        <v>-11.68511230458133</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.738347823774959</v>
+        <v>-6.192002107019015</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.340478343350526</v>
+        <v>-7.350907979048678</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>80</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-6.485964314126619</v>
+        <v>-6.473054504550568</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-16.40464254453273</v>
+        <v>-16.39163541311513</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-15.08391322144904</v>
+        <v>-15.07093407905057</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-16.8128106269974</v>
+        <v>-16.79969982262246</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-21.2772734511865</v>
+        <v>-21.26423055489214</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-14.21915002560164</v>
+        <v>-14.20608377130116</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-13.49585723390694</v>
+        <v>-13.4826762246117</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-13.55685712008924</v>
+        <v>-13.54365838113448</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-17.51943210431396</v>
+        <v>-17.96500574889291</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-11.15645107658922</v>
+        <v>-11.68663174937915</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.095870990607843</v>
+        <v>-8.669591240279779</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.664273749700882</v>
+        <v>-2.329730049028299</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.664552417424602</v>
+        <v>-2.674982053122754</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that WR Spread-7-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that WR Spread-7-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.60179977502812</v>
+        <v>10.61432206470374</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.418797590635293</v>
+        <v>5.431707400211344</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.214405074514886</v>
+        <v>6.227412205932488</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.48751534997954</v>
+        <v>13.500494492378</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>17.71099889681213</v>
+        <v>17.72410970118707</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>21.57986940595636</v>
+        <v>21.59291230225072</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19.1141833077317</v>
+        <v>19.12724956203218</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>17.45652371847401</v>
+        <v>17.46970472776925</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>17.39552383229171</v>
+        <v>17.40872257124647</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>17.53112151342239</v>
+        <v>17.54457880713261</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.37502848029163</v>
+        <v>16.38848076901174</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>15.95477386934673</v>
+        <v>15.96832991569833</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>17.39497139209921</v>
+        <v>17.38454175640106</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.851389265996922</v>
+        <v>7.863911555672544</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5.377746687515426</v>
+        <v>5.390656497091477</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.982877980918836</v>
+        <v>4.995885112336438</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.8717518031815</v>
+        <v>12.88473094557997</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.91953748466106</v>
+        <v>14.932648289036</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>17.80318631892844</v>
+        <v>17.8162292152228</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16.85638363613892</v>
+        <v>16.8694498904394</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.52713127184018</v>
+        <v>15.54031228113542</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.46613138565788</v>
+        <v>15.47933012461264</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>15.47807516614719</v>
+        <v>15.49148029380002</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.6871149452779</v>
+        <v>12.70057223898812</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.99736017158884</v>
+        <v>11.01081246030895</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.57710556064394</v>
+        <v>10.59066160699554</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.41303378947195</v>
+        <v>13.4026041537738</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>146</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.04080825513249</v>
+        <v>5.053330544808112</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.799097655866866</v>
+        <v>4.812007465442917</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.774091962968903</v>
+        <v>5.787099094386505</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.75366016406955</v>
+        <v>12.76663930646802</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.21523894899738</v>
+        <v>12.22834975337232</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.51268088671304</v>
+        <v>12.52572378300741</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.74301566259145</v>
+        <v>11.75608191689193</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.59090075696063</v>
+        <v>10.60408176625587</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.52990087077833</v>
+        <v>10.54309960973309</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.36470719259972</v>
+        <v>10.37811232025255</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.475022361432821</v>
+        <v>9.488479655143038</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.454610998230315</v>
+        <v>7.468063286950425</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.034356387285413</v>
+        <v>7.047912433637016</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.338872240109637</v>
+        <v>9.328442604411485</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>194</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.916818090046434</v>
+        <v>3.929340379722056</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.356526528364235</v>
+        <v>4.369436337940286</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.474478334588156</v>
+        <v>4.487485466005758</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.73293659540078</v>
+        <v>9.745915737799244</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.681694867508092</v>
+        <v>8.694805671883032</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>9.822382906201824</v>
+        <v>9.505000214338637</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.675793518826445</v>
+        <v>7.688859773126921</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.208610120044945</v>
+        <v>7.221791129340183</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.178538068914186</v>
+        <v>8.191736807868949</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.328412883886259</v>
+        <v>7.34181801153909</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.608195642042908</v>
+        <v>6.621652935753126</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.549795294233704</v>
+        <v>3.563247582953814</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.614076765763031</v>
+        <v>2.627632812114634</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.925653768142411</v>
+        <v>4.915224132444258</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>256</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.759479967727771</v>
+        <v>2.772002257403393</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.428061996786859</v>
+        <v>5.44097180636291</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.756928698750578</v>
+        <v>7.76993583016818</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.61091723991839</v>
+        <v>10.62389638231685</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.905180849748938</v>
+        <v>8.918291654123877</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.670643215480169</v>
+        <v>8.437455567027449</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.80465949820789</v>
+        <v>7.817725752508366</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.946851099426389</v>
+        <v>6.960032108721627</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.276476213244088</v>
+        <v>7.289674952198851</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>5.830972703898581</v>
+        <v>5.844429997608799</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.349730861244012</v>
+        <v>2.363183149964122</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.02364874970088948</v>
+        <v>-0.01009270334928658</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.397947582575398</v>
+        <v>1.387517946877246</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>322</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.697457202628243</v>
+        <v>6.710367012204294</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.69765022442671</v>
+        <v>9.710657355844312</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.44518730765149</v>
+        <v>10.45816645004995</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.869041061046246</v>
+        <v>8.685308995719701</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>9.364548494983275</v>
+        <v>9.179525895056273</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.969255771499817</v>
+        <v>8.982322025800293</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.191513366507131</v>
+        <v>8.204694375802369</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.509395467902472</v>
+        <v>7.522594206857235</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.901506307719266</v>
+        <v>7.914911435372098</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.454516958556965</v>
+        <v>6.467974252267183</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.072751047579409</v>
+        <v>3.086203336299519</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.099701405578614</v>
+        <v>1.113257451930217</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.902217768910795</v>
+        <v>2.891788133212643</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>404</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.69375379801663</v>
+        <v>1.706276087692252</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.284150628402124</v>
+        <v>3.297060437978175</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.322779458751342</v>
+        <v>7.335786590168944</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.699338010078058</v>
+        <v>7.712317152476523</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.573432759245989</v>
+        <v>6.435111343223191</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.528007076866309</v>
+        <v>6.390090432762186</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.185847617019768</v>
+        <v>7.198913871320244</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.223614713287773</v>
+        <v>6.236795722583011</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.915090074630228</v>
+        <v>5.928288813584992</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.550113404453782</v>
+        <v>6.563518532106613</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.860211565284722</v>
+        <v>4.87366885899494</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.924297692927176</v>
+        <v>1.937749981647286</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.008993577031781</v>
+        <v>1.022549623383384</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.248813919209056</v>
+        <v>2.238384283510904</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>490</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5553421675949082</v>
+        <v>0.5678644572705309</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.212061237557471</v>
+        <v>3.224971047133522</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.865973018765764</v>
+        <v>5.878980150183367</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.402730216413907</v>
+        <v>6.415709358812371</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.580749648436608</v>
+        <v>5.470915740676034</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.001638113439355</v>
+        <v>5.891234482446635</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.712822763514012</v>
+        <v>5.725889017814488</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.061965895344755</v>
+        <v>6.075146904639993</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.388721111203274</v>
+        <v>5.401919850158038</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.150840824134526</v>
+        <v>5.164245951787358</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.333842601857768</v>
+        <v>4.347299895567986</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.123327800019524</v>
+        <v>2.136780088739634</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.498991556421558</v>
+        <v>1.512547602773161</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.748712888697845</v>
+        <v>1.738283252999693</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>588</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.667306180636054</v>
+        <v>2.679828470311676</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.424598895928987</v>
+        <v>3.437508705505039</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.483170207686811</v>
+        <v>4.396375222611248</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.121897916565487</v>
+        <v>5.134877058963951</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.024039562993707</v>
+        <v>4.935570556715717</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.763542875344108</v>
+        <v>5.674082970857725</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.018945212493598</v>
+        <v>6.032011466794074</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>6.402101949766525</v>
+        <v>6.415282959061763</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.320693900318922</v>
+        <v>5.333892639273685</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.925679336551646</v>
+        <v>3.939136630261864</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.259382221788229</v>
+        <v>2.272834510508339</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.498991556421558</v>
+        <v>1.512547602773161</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.258916970330503</v>
+        <v>2.248487334632351</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>712</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.534494640683882</v>
+        <v>2.547016930359504</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.297222703697273</v>
+        <v>3.310132513273324</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.982636842746658</v>
+        <v>2.915361128518285</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.812190674654858</v>
+        <v>3.825169817053322</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.195592734347144</v>
+        <v>4.126041103118474</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.856433888691946</v>
+        <v>4.786189613175097</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.838367363376427</v>
+        <v>5.766533606645808</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.073431155606173</v>
+        <v>6.08661216490141</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.871981831221618</v>
+        <v>5.885180570176381</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.600508331586951</v>
+        <v>4.613913459239782</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.974406692662619</v>
+        <v>3.987863986372837</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.182947153378841</v>
+        <v>2.196399442098951</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.481793666029454</v>
+        <v>1.495349712381056</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.433762189316965</v>
+        <v>2.423332553618813</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>854</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.576329121650488</v>
+        <v>1.526052610580628</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.075430441680247</v>
+        <v>1.024176946169256</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9779748380846556</v>
+        <v>0.9263977372812349</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.223137953746836</v>
+        <v>2.170158162041666</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.451764361876663</v>
+        <v>2.397944229163954</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.868925379222858</v>
+        <v>3.813651065045562</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.374917109449107</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.727405841815148</v>
+        <v>5.740586851110386</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.31511789942676</v>
+        <v>5.328316638381523</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.050472808075646</v>
+        <v>5.063877935728478</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.026047352610526</v>
+        <v>4.039504646320744</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.889470322602328</v>
+        <v>2.902922611322438</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.000831636715972</v>
+        <v>2.014387683067575</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.953129081404434</v>
+        <v>2.942699445706282</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1037</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.677223233001911</v>
+        <v>1.637857915825805</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6934525581885325</v>
+        <v>0.6538230921256982</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3512240672416667</v>
+        <v>0.3115909830095447</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.111141723605911</v>
+        <v>1.070825218328324</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9148579187654633</v>
+        <v>0.8742928513702211</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.422148514131422</v>
+        <v>2.380299441899659</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.646028832826985</v>
+        <v>3.602889529001622</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.432461634624076</v>
+        <v>4.445642643919314</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.757189810158259</v>
+        <v>4.770388549113022</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.389224702275953</v>
+        <v>4.402629829928784</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.220151223667145</v>
+        <v>3.233608517377363</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.615190118717486</v>
+        <v>1.628642407437596</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.677095584918206</v>
+        <v>1.690651631269809</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.312544978910978</v>
+        <v>2.302115343212826</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1281</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.197315370543713</v>
+        <v>1.168152292447012</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6383784245240562</v>
+        <v>0.6087525772565243</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.05264854310855327</v>
+        <v>0.0232353563435197</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.237849128350696</v>
+        <v>1.207553969865494</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2751157360653664</v>
+        <v>0.2452489980272929</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.707645945589377</v>
+        <v>1.676793087612417</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.057196578613819</v>
+        <v>2.025994083241592</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.68290935469571</v>
+        <v>2.696090363990947</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.778037493493891</v>
+        <v>2.791236232448654</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.864680458348872</v>
+        <v>2.878085586001703</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.113479046599593</v>
+        <v>2.126936340309811</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.367222079042605</v>
+        <v>1.380674367762715</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.7908394431172212</v>
+        <v>0.8043954894688241</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.118624787883746</v>
+        <v>1.108195152185594</v>
       </c>
     </row>
     <row r="19">
@@ -4587,98 +4587,98 @@
         <v>1594</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.535293722263482</v>
+        <v>1.514090211662896</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.019988066825768</v>
+        <v>0.9984662711551024</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4094376841816469</v>
+        <v>0.3881264916467728</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7617867606714626</v>
+        <v>0.740287219975599</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4457396309266883</v>
+        <v>0.4242110183096628</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.09114760144508</v>
+        <v>1.069311503133328</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.919079560903818</v>
+        <v>1.896673120929414</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.491177479602051</v>
+        <v>2.468211967655797</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.806589136707075</v>
+        <v>2.819787875661838</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.521081266610139</v>
+        <v>2.53448639426297</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.877181141790679</v>
+        <v>1.890638435500897</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.221476469776</v>
+        <v>1.23492875849611</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5502808299728912</v>
+        <v>0.5638368763244941</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6117963906055124</v>
+        <v>0.6013667549073602</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.0001886</t>
+          <t>X &lt; 0.0001913</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2548</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9312192140366022</v>
+        <v>0.9228398380102476</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1628032586816843</v>
+        <v>0.1544732188675724</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.249978563781788</v>
+        <v>-0.2582125843125027</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2933818972253945</v>
+        <v>0.2849497550941322</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.02760967872313813</v>
+        <v>-0.03600374858155675</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7227265488135046</v>
+        <v>0.7140786049144765</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.326628897972505</v>
+        <v>1.317725752508373</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.666361499740354</v>
+        <v>1.65724792865101</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.76234748482964</v>
+        <v>1.775546223784403</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.814891059613331</v>
+        <v>1.828296187266162</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.649384203113655</v>
+        <v>1.662841496823873</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.448288553551698</v>
+        <v>1.461740842271809</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.381252152967868</v>
+        <v>1.394808199319471</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.473987613972568</v>
+        <v>1.463557978274416</v>
       </c>
     </row>
     <row r="21">
@@ -4691,46 +4691,46 @@
         <v>2872</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9626228121276412</v>
+        <v>0.9565839694656546</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2730283725936644</v>
+        <v>0.2670503599030383</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2794033365934467</v>
+        <v>0.2733766653785423</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4634740227393195</v>
+        <v>0.4573940405184231</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1254400265833198</v>
+        <v>-0.1313774171651474</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2954474952296522</v>
+        <v>0.2893926335136641</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7519271626701212</v>
+        <v>0.7457007003162985</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8959719211534036</v>
+        <v>0.8896407495152232</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.252799333021251</v>
+        <v>1.265998071976014</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8901393290518129</v>
+        <v>0.903544456704644</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8594807122551273</v>
+        <v>0.8729380059653451</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6153123375671257</v>
+        <v>0.6287646262872357</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4736092586556566</v>
+        <v>0.4871653050072595</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.5492358834110505</v>
+        <v>0.5388062477128983</v>
       </c>
     </row>
     <row r="22">
@@ -4743,46 +4743,46 @@
         <v>3091</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.928123978046969</v>
+        <v>0.9234079449416086</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2379005627896049</v>
+        <v>0.2332690836322868</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5065793085495969</v>
+        <v>0.5018252323636005</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5899847707042056</v>
+        <v>0.5852121003514199</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.004685602263542421</v>
+        <v>5.400459502169497e-05</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4815367654316702</v>
+        <v>0.4767735390531413</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.061451218777101</v>
+        <v>1.056490705628313</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.065234106543826</v>
+        <v>1.060230200571567</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.618922023661426</v>
+        <v>1.632120762616189</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.318780662638673</v>
+        <v>1.332185790291504</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.243435296910555</v>
+        <v>1.256892590620772</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.7925386095455309</v>
+        <v>0.805990898265641</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.7281558847216232</v>
+        <v>0.7417119310732261</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7514132894663703</v>
+        <v>0.7409836537682182</v>
       </c>
     </row>
     <row r="23">
@@ -4795,46 +4795,46 @@
         <v>3258</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.044080822209622</v>
+        <v>1.040210730029024</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1229292432963547</v>
+        <v>0.1192301888061138</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.60278561827392</v>
+        <v>0.5989108053722774</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.6579629281524291</v>
+        <v>0.6540779607025016</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1670816058847109</v>
+        <v>0.1633085566949291</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.450742908731705</v>
+        <v>0.4469009998456741</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.027273797072574</v>
+        <v>1.023247224901006</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9762115199297625</v>
+        <v>0.9721667742632079</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.344923113182709</v>
+        <v>1.358121852137472</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9245094075900155</v>
+        <v>0.9379145352428466</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.8732244687850113</v>
+        <v>0.886681762495229</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4165087924901769</v>
+        <v>0.429961081210287</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3338846296729656</v>
+        <v>0.3474406760245685</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3380565451291204</v>
+        <v>0.3276269094309683</v>
       </c>
     </row>
     <row r="24">
@@ -4847,46 +4847,46 @@
         <v>3378</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.036842329716166</v>
+        <v>1.033555322094116</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1798580431851065</v>
+        <v>0.1767309635510088</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6582630197030142</v>
+        <v>0.6549704632779907</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.7161205708969902</v>
+        <v>0.712816607153556</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2827232387228023</v>
+        <v>0.279515068538025</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4485648131133075</v>
+        <v>0.4453228316798814</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.9424221498799881</v>
+        <v>0.9390275276562932</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9949657382659396</v>
+        <v>0.9915271886269323</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.289205638939762</v>
+        <v>1.302404377894526</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.031146765338718</v>
+        <v>1.044551892991549</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.8263934410211391</v>
+        <v>0.8398507347313569</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7127600205098474</v>
+        <v>0.7262123092299575</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4701253029930186</v>
+        <v>0.4836813493446215</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4238134795558537</v>
+        <v>0.4133838438577015</v>
       </c>
     </row>
     <row r="25">
@@ -4899,46 +4899,46 @@
         <v>3501</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.098351873632673</v>
+        <v>1.095601495826436</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.3860060308976188</v>
+        <v>0.383382483015275</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.9764456580044225</v>
+        <v>0.9736340479627188</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.065465217515701</v>
+        <v>1.062632867408553</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6855585837005833</v>
+        <v>0.6828081591722537</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.7419481683776823</v>
+        <v>0.7391941026421165</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.101347105289555</v>
+        <v>1.098485101637685</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.021423543013931</v>
+        <v>1.018561163547439</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.246056333209815</v>
+        <v>1.259255072164578</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.9957597685760575</v>
+        <v>1.009164896228889</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.9909493177232065</v>
+        <v>1.004406611433424</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9396426721551805</v>
+        <v>0.9530949608752906</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.5479513288480931</v>
+        <v>0.561507375199696</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4834767171083882</v>
+        <v>0.4730470814102361</v>
       </c>
     </row>
     <row r="26">
@@ -4951,46 +4951,46 @@
         <v>3592</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.07699791207677</v>
+        <v>1.074639525021205</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5364555487601734</v>
+        <v>0.5341829555904809</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.01860698880855</v>
+        <v>1.016183745676798</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.080873049010201</v>
+        <v>1.078436428118103</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.8638567019647851</v>
+        <v>0.8614580776900596</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.9263993367934731</v>
+        <v>0.9239938308287705</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.191105365171431</v>
+        <v>1.188621690182266</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.12923556490523</v>
+        <v>1.126749510614189</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.290952827943414</v>
+        <v>1.304151566898177</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.108979090576959</v>
+        <v>1.12238421822979</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.01558434086963</v>
+        <v>1.029041634579848</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.9664485672573804</v>
+        <v>0.9799008559774904</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.6853921745752842</v>
+        <v>0.6989482209268871</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.628877426673391</v>
+        <v>0.6184477909752388</v>
       </c>
     </row>
     <row r="27">
@@ -5003,46 +5003,46 @@
         <v>3684</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7983525223801067</v>
+        <v>0.7964404158361731</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3665327822729196</v>
+        <v>0.3646846550525851</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.8267661479765351</v>
+        <v>0.8247796081779484</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8635612130102075</v>
+        <v>0.861567954020714</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.7198330244420319</v>
+        <v>0.7178603467815279</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.7881995095658993</v>
+        <v>0.786216963415427</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.9084586840966224</v>
+        <v>0.9064398056825382</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.8635347313482171</v>
+        <v>0.8615119255465871</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.9925457029292133</v>
+        <v>1.005744441883976</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9296083572063907</v>
+        <v>0.9430134848592218</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.8605770741483099</v>
+        <v>0.8740343678585276</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.7592381902342424</v>
+        <v>0.7726904789543525</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5561388453045453</v>
+        <v>0.5696948916561482</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5615605033137285</v>
+        <v>0.5511308676155764</v>
       </c>
     </row>
     <row r="28">
@@ -5055,46 +5055,46 @@
         <v>3759</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7726264700183876</v>
+        <v>0.7710085779073808</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.370419673731476</v>
+        <v>0.3688644191527501</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.8136156407817765</v>
+        <v>0.8119312725232746</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8256953735169859</v>
+        <v>0.8240105087739309</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.5677620167331412</v>
+        <v>0.5661303787113283</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.7204221971339848</v>
+        <v>0.7187572175693191</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7567871577823553</v>
+        <v>0.7551094270630045</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8896176264282545</v>
+        <v>0.8878911512748218</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.041440299437227</v>
+        <v>1.05463903839199</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.9893997113765707</v>
+        <v>1.002804839029402</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.9176604865535438</v>
+        <v>0.9311177802637616</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.7126182648087962</v>
+        <v>0.7260705535289063</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.6648031324486183</v>
+        <v>0.6783591788002212</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.6484962657358082</v>
+        <v>0.6380666300376561</v>
       </c>
     </row>
     <row r="29">
@@ -5107,46 +5107,46 @@
         <v>3827</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5060400313810476</v>
+        <v>0.5047423788528747</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.34320095490299</v>
+        <v>0.3419093526668178</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.7454220742166555</v>
+        <v>0.7440161342243954</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7595815766268075</v>
+        <v>0.7581741822080019</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.4705413560934915</v>
+        <v>0.4691967728207374</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.677980313939301</v>
+        <v>0.6765875478058589</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.7121830091796824</v>
+        <v>0.7107787689617524</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.7559500999489899</v>
+        <v>0.754523357415458</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.8778611100300893</v>
+        <v>0.8910598489848525</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.8639000222062307</v>
+        <v>0.8773051498590618</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.789797338076788</v>
+        <v>0.8032546317870057</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.6151394711212035</v>
+        <v>0.6285917598413135</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.4039258844773173</v>
+        <v>0.4174819308289202</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.4968664485278467</v>
+        <v>0.4864368128296945</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3887</v>
+        <v>3888</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3299703040200086</v>
+        <v>0.3289377031069094</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.246721057839892</v>
+        <v>0.245680217264244</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.6105456570961536</v>
+        <v>0.6094037702090347</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.7549550769620268</v>
+        <v>0.7537779321021176</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.5133284617316178</v>
+        <v>0.5122031044872557</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.696512208027066</v>
+        <v>0.69534464209314</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.7545309635035196</v>
+        <v>0.7533464155769849</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.7387360634274174</v>
+        <v>0.7375465688758709</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.8721552255897649</v>
+        <v>0.8709297734896637</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.8965156372696583</v>
+        <v>0.9099207649224894</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.7946429713882921</v>
+        <v>0.8081002650985099</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.6747051410794001</v>
+        <v>0.6881574297995101</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.5630925054431373</v>
+        <v>0.5766485517947402</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5445419998637888</v>
+        <v>0.5451825559307437</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3939</v>
+        <v>3940</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3181118317657052</v>
+        <v>0.3172607230741562</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3160673675604997</v>
+        <v>0.3151927092285689</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.5938851990533038</v>
+        <v>0.592933940341986</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7127552558278083</v>
+        <v>0.7117753554581583</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.54326973618236</v>
+        <v>0.5423244395539015</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.5504381051580793</v>
+        <v>0.5494949353039473</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.5811688843063152</v>
+        <v>0.5802162419833792</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.610122635838465</v>
+        <v>0.6091553329732804</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.7663239289801282</v>
+        <v>0.765315652528713</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.7791429063887563</v>
+        <v>0.7925480340415874</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.701293135370662</v>
+        <v>0.7147504290808797</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.608772739416608</v>
+        <v>0.6222250281367181</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.518467367050377</v>
+        <v>0.5320234134019799</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.5034470748323159</v>
+        <v>0.5039519570295354</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3987</v>
+        <v>3988</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.359414532642873</v>
+        <v>0.3587136917573588</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3130105949859683</v>
+        <v>0.3123022808062217</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6077808524675348</v>
+        <v>0.6069938258144916</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.6516597455288888</v>
+        <v>0.6508629021354935</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5528731214518814</v>
+        <v>0.5520943886758829</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5635350345731283</v>
+        <v>0.5627567530571014</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4926294230199204</v>
+        <v>0.4918675716013254</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.4905219755858212</v>
+        <v>0.4897548530825233</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.6190037959923345</v>
+        <v>0.6182034054452785</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.6715867353375273</v>
+        <v>0.6849918629903584</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.6172847650821325</v>
+        <v>0.6307420587923502</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.5262917940424074</v>
+        <v>0.5397440827625175</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3317142141907823</v>
+        <v>0.3452702605423852</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4452419141530299</v>
+        <v>0.4456297823837687</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4026</v>
+        <v>4027</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.3442320639288141</v>
+        <v>0.3436627603477049</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.133956832319079</v>
+        <v>0.1334245182853309</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.496400044583261</v>
+        <v>0.4957739879283949</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.5162851912493736</v>
+        <v>0.5156551313918456</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5372502110316901</v>
+        <v>0.5366097011870608</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.5506835380608166</v>
+        <v>0.5500421648630933</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4548208285628235</v>
+        <v>0.4542021793073729</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.473027241432348</v>
+        <v>0.4723994765548341</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.5003401317938767</v>
+        <v>0.4997047436586328</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.5690130595049681</v>
+        <v>0.5824181871577991</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.5132540237396555</v>
+        <v>0.5267113174498732</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.448307655383573</v>
+        <v>0.461759944103683</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2515444772670747</v>
+        <v>0.2651005236186776</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2918559283280118</v>
+        <v>0.2921771224421832</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.310299997547034</v>
+        <v>0.309838825624972</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2861319782648764</v>
+        <v>0.2856647234259171</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.544410698811852</v>
+        <v>0.5438767991498565</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.5651497510202859</v>
+        <v>0.5646114777548306</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.5326208986409213</v>
+        <v>0.5320864483712953</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.6220945205774342</v>
+        <v>0.6215400014840355</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.4770732913113349</v>
+        <v>0.476553627416024</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.5162147049942689</v>
+        <v>0.5156817392634991</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.5182209150676442</v>
+        <v>0.517686777771651</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6045176127405512</v>
+        <v>0.6179227403933822</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4983350129177992</v>
+        <v>0.511792306628017</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.4587901268921115</v>
+        <v>0.4722424156122216</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.309605008307976</v>
+        <v>0.3231610546595789</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3268821401302446</v>
+        <v>0.3271125747727552</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4085</v>
+        <v>4086</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1445685190670218</v>
+        <v>0.1442365946182775</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2560923912821593</v>
+        <v>0.255723963358335</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4121428206397297</v>
+        <v>0.4117338700977911</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4091551865545995</v>
+        <v>0.4087475296632874</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.4464745051483732</v>
+        <v>0.4460545045300606</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.5618070085836138</v>
+        <v>0.5613603171535146</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.4416457995777492</v>
+        <v>0.4412278312562208</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.4039062437865582</v>
+        <v>0.4034946821071443</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.4299270208799157</v>
+        <v>0.4295085709901443</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.5098067306145921</v>
+        <v>0.5232118582674232</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.3784748453572178</v>
+        <v>0.3919321390674355</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.314962750622378</v>
+        <v>0.3284150393424881</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1883938959183027</v>
+        <v>0.2019499422699056</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1827548041176215</v>
+        <v>0.1829474622957434</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/williams_r/wr_spread_7_14.xlsx
+++ b/workspaces/btc_daily_14days/williams_r/wr_spread_7_14.xlsx
@@ -568,885 +568,885 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.3697</t>
+          <t>X ≈ -0.3695</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>32</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.6413907722427226</v>
+        <v>0.6122993029322075</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.267324955263234</v>
+        <v>5.266183715454908</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.758208590181518</v>
+        <v>1.7580692893671</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.24015923530981</v>
+        <v>11.23974333393787</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.58761667035548</v>
+        <v>7.636101410167704</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.886228578224973</v>
+        <v>7.910183267083411</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.92342483225646</v>
+        <v>10.97140525532306</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.45981662017908</v>
+        <v>10.50903357311933</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.4015783679487</v>
+        <v>10.47477937355251</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.433169838649377</v>
+        <v>6.532435535549595</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.01508656306442901</v>
+        <v>0.0847467673251856</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.104124109580773</v>
+        <v>-2.980493484769376</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.524889986774539</v>
+        <v>-3.376240038582189</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.950017946877246</v>
+        <v>3.122016706443908</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.3423</t>
+          <t>X ≈ -0.3421</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.796166127887226</v>
+        <v>-5.825312511298101</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.566812673240086</v>
+        <v>2.565650852758473</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.822136918167608</v>
+        <v>8.822050642733188</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.27880739193528</v>
+        <v>12.2784009130482</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.767045408127167</v>
+        <v>1.815494460819743</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.915907684707179</v>
+        <v>-7.892038001149366</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-8.002251020002255</v>
+        <v>-7.954360039771863</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-8.470506805127044</v>
+        <v>-8.421366643562038</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-8.53340597695167</v>
+        <v>-8.460269470189388</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-9.384526073792252</v>
+        <v>-9.285304261055423</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.929580417591083</v>
+        <v>-2.82975416024977</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.227547916166074</v>
+        <v>-6.103922604990032</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.649100054313053</v>
+        <v>-6.500452870114792</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293554571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.3149</t>
+          <t>X ≈ -0.3147</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.593500405355428</v>
+        <v>1.484514882731425</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.106602178715114</v>
+        <v>3.894822364826133</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.6288382139959623</v>
+        <v>1.508438302206926</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7659002423606864</v>
+        <v>1.637837186733378</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.861758867982289</v>
+        <v>-0.845253012015533</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5203147811432913</v>
+        <v>1.422876048714492</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.674519979102875</v>
+        <v>-4.62661207864609</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.061771457034112</v>
+        <v>-3.095817368044429</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.038079989236557</v>
+        <v>0.8615595674647309</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.891893783528808</v>
+        <v>-1.9591526808073</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.096836156556506</v>
+        <v>-2.163550355576689</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.30977351333798</v>
+        <v>-8.102859132753998</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-10.81468621675366</v>
+        <v>-10.49941670164822</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-8.508315386456083</v>
+        <v>-8.252983293557911</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.2875</t>
+          <t>X ≈ -0.2873</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.8658822578988179</v>
+        <v>-1.685452491119683</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.786159190989885</v>
+        <v>8.176460631100248</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>18.04725100323217</v>
+        <v>17.59431848483659</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13.35368601831444</v>
+        <v>12.82227805719972</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.600888378898837</v>
+        <v>9.066449010668144</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.070173851737565</v>
+        <v>4.43302672480845</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.205864466327974</v>
+        <v>7.646769769035465</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.131230112958676</v>
+        <v>5.54681295720674</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.461077238660259</v>
+        <v>3.874071656175985</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.613274377965006</v>
+        <v>3.052176539657815</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.409732115986493</v>
+        <v>2.849049009420092</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.391153343156013</v>
+        <v>-2.007494777276797</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.26149985760749</v>
+        <v>-8.958752174972496</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.650788504735658</v>
+        <v>-10.35134394929231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.2601</t>
+          <t>X ≈ -0.2599</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.289376296618293</v>
+        <v>4.191629725532202</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11.72734413513351</v>
+        <v>11.54169800514567</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>17.37966732972252</v>
+        <v>17.10470532332431</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.958306166079844</v>
+        <v>9.795005365823698</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.901686011827096</v>
+        <v>7.820782545892435</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>12.04639494235245</v>
+        <v>11.07416181311025</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13.47436042661107</v>
+        <v>12.50657104294368</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>13.01166157922521</v>
+        <v>12.04484212198883</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.414678598344949</v>
+        <v>7.53931449094938</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>13.62227961969097</v>
+        <v>12.6823915810411</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.879467815533161</v>
+        <v>8.007666815969955</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.887585472264078</v>
+        <v>5.084526831607491</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.469114158283503</v>
+        <v>4.690827638916694</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.726533098392402</v>
+        <v>7.92612118405517</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.2327</t>
+          <t>X ≈ -0.2326</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>82</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.690330991355644</v>
+        <v>-3.717614250615377</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-10.16379857757247</v>
+        <v>-10.1598947015839</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.044719523760421</v>
+        <v>-2.044181989970454</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.132121756227789</v>
+        <v>-3.131373628943415</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.452509931543631</v>
+        <v>-2.403125734774491</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.590209132930035</v>
+        <v>-4.565244999625278</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1943106396786973</v>
+        <v>0.2422841371128825</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.489311296339523</v>
+        <v>-1.440104911625106</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3324575222693369</v>
+        <v>-0.2592661103335416</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.254964491114819</v>
+        <v>1.354233831505027</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.386091715190574</v>
+        <v>-1.286248058817485</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.57071373498615</v>
+        <v>-2.447075975039184</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6661975996534508</v>
+        <v>0.814852407021263</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3274210775129944</v>
+        <v>-0.1554223179463321</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.2053</t>
+          <t>X ≈ -0.2052</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>86</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.792640197938901</v>
+        <v>-4.819249556613116</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.876215262330732</v>
+        <v>2.873379572591872</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.997791999399972</v>
+        <v>-0.9977836859148823</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2923054996875507</v>
+        <v>0.2912741724784809</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9161599486793648</v>
+        <v>0.9637736591829835</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.534191038519182</v>
+        <v>3.557037907250503</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.192791569714181</v>
+        <v>-1.144826085499815</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.306244954520736</v>
+        <v>5.355476344148528</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.924590145389345</v>
+        <v>2.997789391656696</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.408133294038464</v>
+        <v>-1.308874366991262</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.872771582611264</v>
+        <v>1.972618706844045</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.070066451634126</v>
+        <v>3.193708874077892</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.81337735066537</v>
+        <v>3.962032682673502</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6110285647506615</v>
+        <v>-0.4390298051839991</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.1779</t>
+          <t>X ≈ -0.1778</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13.27339394444669</v>
+        <v>13.09878917801706</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.530475363216496</v>
+        <v>4.476609209221785</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.989773149034669</v>
+        <v>-2.964925146898096</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.294199152586991</v>
+        <v>-1.828865476488538</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.242322247515908</v>
+        <v>1.713399941906303</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.575891553842055</v>
+        <v>4.001910487629473</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.546693478183791</v>
+        <v>6.967183416899488</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8.101257797122805</v>
+        <v>7.512521179592113</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.986018625607457</v>
+        <v>4.451945245343452</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.100095959986817</v>
+        <v>1.612506101264366</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.896388696374558</v>
+        <v>1.409215786727152</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.95139364821744</v>
+        <v>2.477551197243606</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.512117030291904</v>
+        <v>1.073425053281255</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.799507742795612</v>
+        <v>4.353077312504517</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.1505</t>
+          <t>X ≈ -0.1504</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.93181122884409</v>
+        <v>1.881273167713815</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.725871516919959</v>
+        <v>2.695891757400702</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.107651814687543</v>
+        <v>-4.07609523359352</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.366441336340529</v>
+        <v>-2.352409533616012</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.31139084284316</v>
+        <v>0.3509068439569276</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.6112315386771598</v>
+        <v>0.6231923878023267</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.5514345080163</v>
+        <v>4.554948222312795</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.518649270624358</v>
+        <v>4.091306388741813</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.486050432579034</v>
+        <v>8.050337582897306</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.417829474673965</v>
+        <v>4.033797737696354</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.21485648301114</v>
+        <v>3.831261384310459</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.832773933755618</v>
+        <v>1.492169017223951</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.41336876842233</v>
+        <v>1.097640781795818</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.252437301716135</v>
+        <v>2.947016706443904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.1231</t>
+          <t>X ≈ -0.123</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.573481210448392</v>
+        <v>-3.577027034280619</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-10.46219420715299</v>
+        <v>-10.75558330972804</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-9.076803779728593</v>
+        <v>-9.762281545685461</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.13326250044009</v>
+        <v>-6.841556715420964</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.293315746108959</v>
+        <v>-7.33763138209919</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.076010186119781</v>
+        <v>-2.176200469159589</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.056833995292209</v>
+        <v>1.953467753228132</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.99634855453575</v>
+        <v>2.880449019680597</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.530774007948132</v>
+        <v>1.4459861124162</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.310281265376005</v>
+        <v>6.199433111372741</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.293967302164489</v>
+        <v>3.895545868180406</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.44143673712346</v>
+        <v>6.04870448793001</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.615456951630421</v>
+        <v>3.942639828091409</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.546848932792578</v>
+        <v>5.285478244905448</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.0957</t>
+          <t>X ≈ -0.09562</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>183</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.159040838755935</v>
+        <v>2.125966090963018</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.084775756216715</v>
+        <v>-1.084673619153065</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.569659469275109</v>
+        <v>-2.56741448648296</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.076448629447789</v>
+        <v>-4.074512495476078</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.250022038205252</v>
+        <v>-6.199652590068936</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.317652560924834</v>
+        <v>-4.293605981098729</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.40288205462118</v>
+        <v>-4.355843083006874</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.596902678141952</v>
+        <v>-1.547760600245248</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.161375810818406</v>
+        <v>2.236800492558835</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.313701178586513</v>
+        <v>1.414598762770034</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5275493981715229</v>
+        <v>-0.4274467100032098</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.315596541769729</v>
+        <v>-4.194301922996821</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1797213999963461</v>
+        <v>0.3285729373245871</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6872771350899711</v>
+        <v>-0.5152783755233088</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.06831</t>
+          <t>X ≈ -0.06824</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>244</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8409027023954749</v>
+        <v>-0.8693908619913842</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4151127042466456</v>
+        <v>0.4133423418882316</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.205688331737711</v>
+        <v>-1.204496767477607</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.786707023232395</v>
+        <v>1.784979319283792</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.431194110280586</v>
+        <v>-2.381860662561841</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.317437930204605</v>
+        <v>-1.293367334131773</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.674628013262016</v>
+        <v>-4.627829359506549</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.732380162071287</v>
+        <v>-4.685433452382327</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.612827534439596</v>
+        <v>-5.542481962881347</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.597981087063374</v>
+        <v>-3.500263422379767</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.574646809147822</v>
+        <v>-2.475935398937857</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3263497273699798</v>
+        <v>0.4505068201726914</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.961290339407611</v>
+        <v>-2.813503565407423</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.96596565968013</v>
+        <v>-3.793966900113467</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.04091</t>
+          <t>X ≈ -0.04086</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.937372747084467</v>
+        <v>3.170508981749329</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.599157714306038</v>
+        <v>2.542107739150147</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.884783269245155</v>
+        <v>1.836136631567797</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.172903602792971</v>
+        <v>-1.189940691398583</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.157418087262052</v>
+        <v>1.163343090793987</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.413905494204997</v>
+        <v>-1.406897138895374</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.371247724974737</v>
+        <v>1.374572785355966</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.541744210722861</v>
+        <v>1.541676418660309</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.928956235194221</v>
+        <v>2.7700237216376</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.124858956406484</v>
+        <v>0.9996020531525147</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.921633013138397</v>
+        <v>0.7964199882799079</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6376404804730456</v>
+        <v>0.222243695042998</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4205753096305003</v>
+        <v>-0.4893699277234234</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.472905375806455</v>
+        <v>-1.506147850518111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.01351</t>
+          <t>X ≈ -0.01347</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.0726002271995938</v>
+        <v>-0.2040712410604897</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.259335298833683</v>
+        <v>-1.251898753494139</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.338458215006888</v>
+        <v>-1.328815084220139</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.477697305817756</v>
+        <v>-0.4694279260956051</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8047177206396654</v>
+        <v>-0.7467221277230749</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1176172787368657</v>
+        <v>0.1513575964433329</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.345208084508684</v>
+        <v>0.4039349286565113</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2963740412847287</v>
+        <v>0.3582411722900787</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.02603549137030114</v>
+        <v>0.1122847580923647</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6434870047623917</v>
+        <v>0.7593690495562129</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.278139619566041</v>
+        <v>1.396606037905656</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.837797996805527</v>
+        <v>2.08640708191674</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.781462481421769</v>
+        <v>2.951753357033603</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.904158408093188</v>
+        <v>3.095756202242228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.01389</t>
+          <t>X ≈ 0.01392</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>324</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.212682001307641</v>
+        <v>1.17225596807905</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.150623817309231</v>
+        <v>1.14558662619234</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.448857563178798</v>
+        <v>4.43741911178288</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.808439506972512</v>
+        <v>1.803995654068423</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8779961564478569</v>
+        <v>-0.82760171898164</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.045708633559777</v>
+        <v>-3.019569535535041</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.748410033043299</v>
+        <v>-3.700110694932292</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.138314928633989</v>
+        <v>-5.090944303474522</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.739902430097146</v>
+        <v>-2.666961183702504</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.356915174505581</v>
+        <v>-6.263529820854806</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.331814474271596</v>
+        <v>-5.236744473424913</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.91573298324721</v>
+        <v>-5.798228253698987</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.64697355507149</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.733624028431429</v>
+        <v>-6.561625268864738</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.04129</t>
+          <t>X ≈ 0.0413</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>219</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4753397865891245</v>
+        <v>0.659395651846296</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2107942916750289</v>
+        <v>-0.07391793504302058</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.486066688004307</v>
+        <v>3.621690452483101</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.250632379233267</v>
+        <v>2.852817805534379</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.720896414367822</v>
+        <v>1.87481771169967</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.921938488226893</v>
+        <v>3.784828057791799</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.105842826524956</v>
+        <v>6.02396775410525</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.275609526946035</v>
+        <v>3.976378321303876</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>6.392968903874667</v>
+        <v>6.927635996271043</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.922061851493652</v>
+        <v>7.252229743554302</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>6.270597562935563</v>
+        <v>6.384836360533846</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.122667631186019</v>
+        <v>3.253860364599724</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.075536854193125</v>
+        <v>4.228565451734482</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.392369545050705</v>
+        <v>3.564368304617425</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.06869</t>
+          <t>X ≈ 0.06868</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>167</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.176046179887251</v>
+        <v>2.849756673410567</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.986474022370906</v>
+        <v>-2.310984450821785</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.379896784576808</v>
+        <v>2.069033863986398</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.913077608626082</v>
+        <v>1.606071715482926</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.173527196452561</v>
+        <v>2.903775427139195</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1108576123264697</v>
+        <v>-0.4046436772380488</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3918418503602226</v>
+        <v>0.1431391498012289</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6687215612234141</v>
+        <v>-0.3254632793851613</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.715432394261988</v>
+        <v>-3.347584924400266</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.345934109373815</v>
+        <v>-5.977791498534749</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.955837925371</v>
+        <v>-5.585345285903728</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.519412770793544</v>
+        <v>-6.406271426612527</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.944166287795483</v>
+        <v>-6.801429353176253</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.323185645937023</v>
+        <v>-7.151186886370468</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>120</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8241487775918586</v>
+        <v>0.3951251339701187</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.731039117279543</v>
+        <v>1.28343682148644</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.154678369224726</v>
+        <v>2.562033367313099</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.283522314513107</v>
+        <v>2.699128449056161</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.415893393168311</v>
+        <v>3.863491298768871</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3933547329519129</v>
+        <v>0.8129726600385538</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.359253861465149</v>
+        <v>-1.300929235167935</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.489446589699519</v>
+        <v>1.566571337782008</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2352902070740583</v>
+        <v>-0.1370679380214455</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.906418392268009</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4393725519875318</v>
+        <v>-0.33170363303919</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>8.745090404102434</v>
+        <v>8.89312977099241</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.176623585912715</v>
+        <v>4.33130517776187</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.741684613543867</v>
+        <v>2.913683373110572</v>
       </c>
     </row>
     <row r="24">
@@ -1508,569 +1508,569 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.750554335777601</v>
+        <v>3.18429776663686</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.024302902604084</v>
+        <v>5.717448754541273</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>9.650119991223612</v>
+        <v>9.412531074485386</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.58540389967188</v>
+        <v>10.37781126304429</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>11.67887649055131</v>
+        <v>12.36672275600358</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.741899407971516</v>
+        <v>9.360819750232352</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.415309375010374</v>
+        <v>6.021475136416676</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.721418180488946</v>
+        <v>1.457281720295626</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.03808458184109043</v>
+        <v>-0.2190351511362039</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.01520310411478931</v>
+        <v>-0.2231916008036521</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.486343515512971</v>
+        <v>5.310372869693047</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.155609774526219</v>
+        <v>7.007883869353023</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.692925299757718</v>
+        <v>2.51436528705149</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.111603312730857</v>
+        <v>1.943738017919316</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.1509</t>
+          <t>X ≈ 0.1508</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.215545860885392</v>
+        <v>-0.3709349867766605</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.281795625599258</v>
+        <v>6.736308069129706</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.593012038008247</v>
+        <v>3.09573277637358</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.629959052513065</v>
+        <v>2.152582191047316</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>7.650049381592829</v>
+        <v>7.110129741035649</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>7.943556734250123</v>
+        <v>7.382915259854578</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.576434203081362</v>
+        <v>4.061389605411733</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.205221473029965</v>
+        <v>5.769469888506706</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.956394166014185</v>
+        <v>3.558584235891594</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.410262829410726</v>
+        <v>5.995625220293995</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.944080221391374</v>
+        <v>2.530615207540521</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.990122484783818</v>
+        <v>2.588781944905413</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.97276196360864</v>
+        <v>6.541450105298161</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.212380584239881</v>
+        <v>6.790494967313528</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.1783</t>
+          <t>X ≈ 0.1782</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>92</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-10.05316431394233</v>
+        <v>-10.08686552968961</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.226850146805468</v>
+        <v>-6.242320642861458</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.651766261729733</v>
+        <v>-6.65662439056311</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-7.600884360841576</v>
+        <v>-7.614510075173186</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.892278088727942</v>
+        <v>-4.846391998094745</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.600223717358048</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-10.07810385128198</v>
+        <v>-10.06904517719697</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-9.462282813525022</v>
+        <v>-9.447921415841179</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-10.60792787101322</v>
+        <v>-10.57185054671714</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-6.058819890381038</v>
+        <v>-5.9608965188364</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.178815801987547</v>
+        <v>-5.078080444633422</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-7.308010006900886</v>
+        <v>-7.193826750746737</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.474284180980071</v>
+        <v>-4.328115112093322</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.077155966166167</v>
+        <v>-1.905157206599696</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.2057</t>
+          <t>X ≈ 0.2056</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>75</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5463054765182846</v>
+        <v>-0.5577383327986141</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.546587960996149</v>
+        <v>0.5588215727044812</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1094529869984555</v>
+        <v>0.152649854949459</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.079965948810937</v>
+        <v>-1.034857566255191</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-6.866928109443684</v>
+        <v>-6.846391998094823</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.62557369664237</v>
+        <v>-2.573606479275853</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.669216294101531</v>
+        <v>-6.634262568501313</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.091255714544175</v>
+        <v>2.23323800444868</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.337457758230173</v>
+        <v>3.529598728645247</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.844435098125686</v>
+        <v>4.039103481163529</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.668673302864008</v>
+        <v>3.834963033627517</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.578637465054733</v>
+        <v>-1.440203562341004</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.993783575423102</v>
+        <v>6.164638511095276</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.908351280210574</v>
+        <v>5.080350039777315</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.2331</t>
+          <t>X ≈ 0.233</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-14.13812520004543</v>
+        <v>-15.09535620032084</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.165452235826464</v>
+        <v>-0.3743782700561624</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.069411061645006</v>
+        <v>-2.272262271838812</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.939185918056644</v>
+        <v>-3.61897934504163</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.884354264665724</v>
+        <v>-5.592660654811198</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.709720728834832</v>
+        <v>-2.334800509126602</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.794431088101</v>
+        <v>-2.395456598352062</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.623251488359124</v>
+        <v>-7.338901299033949</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.151086473166075</v>
+        <v>-8.868411221603544</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.078687092128845</v>
+        <v>-6.707165175552852</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.271363487628655</v>
+        <v>-6.911305623088943</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.762150718768297</v>
+        <v>-5.360601572291216</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-13.97626556955453</v>
+        <v>-14.71098337945206</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-7.89557028841687</v>
+        <v>-8.4917892637053</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.2605</t>
+          <t>X ≈ 0.2604</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-10.55562611021677</v>
+        <v>-7.973935838692853</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.7116406845551</v>
+        <v>-5.686950496419342</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.713310131460865</v>
+        <v>-7.616783602415921</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4973707730855068</v>
+        <v>2.033351683640682</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.183794138714823</v>
+        <v>3.883766732063997</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.869673561178764</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.401054354104204</v>
+        <v>4.095896161657421</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2976220259381464</v>
+        <v>0.4554602266709438</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3563059099507839</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.801377439989793</v>
+        <v>2.769262211322342</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.023980596127615</v>
+        <v>0.9778201764845704</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.356389821003319</v>
+        <v>4.210590088452683</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.51440570543603</v>
+        <v>10.16463851109526</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.230755651795278</v>
+        <v>2.477175436602593</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.2879</t>
+          <t>X ≈ 0.2878</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6221195695177997</v>
+        <v>-0.5392438821880532</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.399228315928397</v>
+        <v>5.84531708490119</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7569463279172624</v>
+        <v>-0.515568429166386</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.547188937359088</v>
+        <v>-2.357142857142861</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.651256251830361</v>
+        <v>3.153608001905162</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-10.32196437210793</v>
+        <v>-10.57360647927585</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-12.30247396759887</v>
+        <v>-12.63426256850131</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-8.984111268137397</v>
+        <v>-9.100095328884656</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.180129834442184</v>
+        <v>-7.137067938021453</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.023881501570742</v>
+        <v>-7.960896518836492</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.2999105807219</v>
+        <v>-6.165036966372469</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-4.333757519016075</v>
+        <v>-4.106870229007633</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.817559877012577</v>
+        <v>-2.502028155571509</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.578828206968907</v>
+        <v>-2.252983293556063</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.3153</t>
+          <t>X ≈ 0.3151</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.574387361725563</v>
+        <v>4.482462085719739</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.002100774952523921</v>
+        <v>0.8608935195494283</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.530207236988424</v>
+        <v>1.45790614416223</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-4.490427628978871</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.160365474399363</v>
+        <v>1.153608001905226</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.45773950403445</v>
+        <v>1.426393520724154</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-6.777154005414808</v>
+        <v>-6.634262568501313</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-9.291324098476942</v>
+        <v>-9.100095328884656</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-11.43763035119341</v>
+        <v>-11.13706793802145</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-8.202901910702082</v>
+        <v>-7.960896518836435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.319228579799599</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.2500600274238</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-14.93626557494785</v>
+        <v>-14.50202815557149</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.341648719789418</v>
+        <v>-4.25298329355612</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.3427</t>
+          <t>X ≈ 0.3425</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.373049538052463</v>
+        <v>-1.26921929301087</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-17.80018890860806</v>
+        <v>-18.09602115048001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-10.91762224679429</v>
+        <v>-10.90020236891005</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-13.29514576480072</v>
+        <v>-13.33150183150182</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.294692009922315</v>
+        <v>-1.000238151940913</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9973179802872281</v>
+        <v>-0.7274526331219846</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.512930770455888</v>
+        <v>-3.352211286450036</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.4876199987863</v>
+        <v>-1.253941482730809</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.57959680168827</v>
+        <v>-11.54732434827786</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-9.952505428700306</v>
+        <v>-9.807050364990303</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.11738390268633</v>
+        <v>-10.01119081252637</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.52595389010375</v>
+        <v>-7.388921511058918</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-7.905654572811358</v>
+        <v>-7.784079437622701</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-15.39934102748173</v>
+        <v>-15.2273422679151</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.3701</t>
+          <t>X ≈ 0.3699</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.27347830696759</v>
+        <v>-2.308498921661169</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>19.3747536013221</v>
+        <v>21.57875410070984</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.137985503602572</v>
+        <v>8.640213245011623</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.268210647190934</v>
+        <v>6.933179723502278</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4912770625868035</v>
+        <v>-0.007682320675449716</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.137894202071337</v>
+        <v>9.942522552982183</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.956860810998243</v>
+        <v>3.43025356053095</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.575416220577516</v>
+        <v>6.190227251760504</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.403834985713722</v>
+        <v>2.927448191010811</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.61456521777486</v>
+        <v>5.329426061808746</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.671209967947377</v>
+        <v>-1.326327288953173</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.642189540222226</v>
+        <v>1.95764590002463</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.765001232937905</v>
+        <v>8.014100876686605</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.865340527522406</v>
+        <v>5.037339287089118</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.3975</t>
+          <t>X ≈ 0.3973</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-23.27173235706498</v>
+        <v>-23.93868325345841</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.177136137203632</v>
+        <v>-4.093288910042816</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-18.68755378046207</v>
+        <v>-18.77274118407183</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-21.95868918109138</v>
+        <v>-22.21428571428572</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-12.20786308792858</v>
+        <v>-11.98924914095193</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.636679534483953</v>
+        <v>-8.145035050704408</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-5.022410301913403</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-15.77859459195869</v>
+        <v>-15.81438104317039</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12.39569919746106</v>
+        <v>-12.27992508087862</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-13.37316901419904</v>
+        <v>-13.10375366169358</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-16.83618750134455</v>
+        <v>-16.87932268065821</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-20.30088677401433</v>
+        <v>-20.39258451472192</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-17.22706512984963</v>
+        <v>-17.2163138698572</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-20.71069633883704</v>
+        <v>-20.53869757927038</v>
       </c>
     </row>
   </sheetData>
@@ -2210,833 +2210,833 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.3834</t>
+          <t>X &gt; -0.3832</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1976437472620631</v>
+        <v>-0.1964245379897562</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01146407083269452</v>
+        <v>0.01146139446386485</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05247331289756119</v>
+        <v>-0.05232904260704885</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1777627342663308</v>
+        <v>-0.1772744681591973</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2628186316224728</v>
+        <v>-0.2632618176949748</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3188352818685019</v>
+        <v>-0.3185467377493936</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2435361697220131</v>
+        <v>-0.2440186660622885</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2325131456815015</v>
+        <v>-0.2330545872403533</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2066548740795966</v>
+        <v>-0.2078341654494693</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2354763453547051</v>
+        <v>-0.2371962503472957</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2061934724034415</v>
+        <v>-0.2080057163725257</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1825746854913106</v>
+        <v>-0.185014307151711</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1726378600967706</v>
+        <v>-0.1756969391571985</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.227039867919423</v>
+        <v>-0.230505893116316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.356</t>
+          <t>X &gt; -0.3558</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4050</v>
+        <v>4061</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2042731558112436</v>
+        <v>-0.2027971464382787</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.0300637188714532</v>
+        <v>-0.02994493754099636</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.06677993534164273</v>
+        <v>-0.06659467831824628</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.26797841402594</v>
+        <v>-0.2672386567007123</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3248467624035385</v>
+        <v>-0.325507477210266</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3836654160717003</v>
+        <v>-0.3833877523159117</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3317689480092554</v>
+        <v>-0.33239432857998</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3169957512389203</v>
+        <v>-0.3177004432195503</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2904730132758715</v>
+        <v>-0.2920113713711814</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2881668831048572</v>
+        <v>-0.2905398152693976</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2077034529216704</v>
+        <v>-0.2103125569237037</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1594908381898748</v>
+        <v>-0.1629863993251277</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1461509297131443</v>
+        <v>-0.1504771954532913</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2521425469499121</v>
+        <v>-0.2569232098328698</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.3286</t>
+          <t>X &gt; -0.3284</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4020</v>
+        <v>4031</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.1625426112435022</v>
+        <v>-0.1609525766179445</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.04944339343944648</v>
+        <v>-0.04926219720583447</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1331151357409581</v>
+        <v>-0.1327468389809923</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3616111439211807</v>
+        <v>-0.3606073461307417</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3404578980045088</v>
+        <v>-0.3414415030452744</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3274546528729303</v>
+        <v>-0.3275059593451815</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2745265444869176</v>
+        <v>-0.2756692054502992</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2561486538218389</v>
+        <v>-0.2573903499398966</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2289585881738176</v>
+        <v>-0.2312205643841878</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2202836055624218</v>
+        <v>-0.2235978819095408</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1873909382599592</v>
+        <v>-0.1908178290398581</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1142068301452781</v>
+        <v>-0.1187720390745781</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.0976214586340447</v>
+        <v>-0.1032186317619335</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2060765804859415</v>
+        <v>-0.2122985999316853</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.3012</t>
+          <t>X &gt; -0.301</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3972</v>
+        <v>3981</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1716790827431893</v>
+        <v>-0.1816190857783155</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.08758291697001397</v>
+        <v>-0.09879855191611142</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.142323031206061</v>
+        <v>-0.1533595636882055</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3752366591632494</v>
+        <v>-0.3857071267494803</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3220735962525154</v>
+        <v>-0.3351138026060596</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3376996007160358</v>
+        <v>-0.3494901593961828</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2213544183888416</v>
+        <v>-0.2210228493438464</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2222438465322654</v>
+        <v>-0.2217406762636358</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2442702326138217</v>
+        <v>-0.2449455095217061</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2000828783362394</v>
+        <v>-0.2017999065403231</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1643160715735945</v>
+        <v>-0.1660409824367832</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01516674938162055</v>
+        <v>-0.01849463272342433</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.03188989795954456</v>
+        <v>0.02735406441849619</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1057474106252698</v>
+        <v>-0.1113103470602326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.2738</t>
+          <t>X &gt; -0.2736</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3910</v>
+        <v>3920</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1606712574593914</v>
+        <v>-0.158217596562551</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2282918711115727</v>
+        <v>-0.2275717177742678</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4307510593736268</v>
+        <v>-0.4295351659739168</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5929331312869337</v>
+        <v>-0.5912395492548228</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4794197963699958</v>
+        <v>-0.481413632098338</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.423451046765166</v>
+        <v>-0.4239119782575216</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3549829531337068</v>
+        <v>-0.3434553365176072</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.3229894694193334</v>
+        <v>-0.3115064343354916</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.3188818804959155</v>
+        <v>-0.3090424603144442</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2605504358530339</v>
+        <v>-0.2524357645041206</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2209889584351572</v>
+        <v>-0.2129594746570049</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.006651963870055511</v>
+        <v>0.01245664503621668</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1633963339813249</v>
+        <v>0.1671888808988271</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.04560618217136181</v>
+        <v>0.04803711460716897</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.2464</t>
+          <t>X &gt; -0.2462</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3844</v>
+        <v>3853</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2370768606251374</v>
+        <v>-0.2338572982444518</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.4335655382323225</v>
+        <v>-0.4322281079729748</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7365490858253239</v>
+        <v>-0.734438906639113</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7740938476309083</v>
+        <v>-0.7718464553825726</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.6233201562401902</v>
+        <v>-0.6257809157540279</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6375535013129721</v>
+        <v>-0.6238525295218977</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5924274544508705</v>
+        <v>-0.5669050555479487</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5519402938757736</v>
+        <v>-0.5263715662518464</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4688337513605134</v>
+        <v>-0.4455179121012875</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4989132828004514</v>
+        <v>-0.4773600915613514</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3772402974262974</v>
+        <v>-0.3559083356671309</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09432140021788626</v>
+        <v>-0.07574182433837251</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.07229920172223814</v>
+        <v>0.08852711168334793</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1034419906877915</v>
+        <v>-0.08895526344968374</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.219</t>
+          <t>X &gt; -0.2189</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3762</v>
+        <v>3771</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1618065685677479</v>
+        <v>-0.1581033682273656</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2214764608198081</v>
+        <v>-0.2207010168363865</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.7080350039777272</v>
+        <v>-0.7059586804834055</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7226961101229463</v>
+        <v>-0.7205387841462993</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5834494593835018</v>
+        <v>-0.5871327388355212</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5513977964239274</v>
+        <v>-0.5381473631075551</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.6095759190225394</v>
+        <v>-0.5845007897824175</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5315084963739096</v>
+        <v>-0.5065025303673139</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4718063326432045</v>
+        <v>-0.4495679380214526</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5371424102489044</v>
+        <v>-0.5171879095649103</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3552504472783227</v>
+        <v>-0.3356781958372821</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.04034368319209847</v>
+        <v>-0.02417741162093989</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.05935404791300414</v>
+        <v>0.072733244216451</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09855993722695189</v>
+        <v>-0.08750994431186143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.1916</t>
+          <t>X &gt; -0.1915</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3676</v>
+        <v>3685</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.05346824100357139</v>
+        <v>-0.04932220887832983</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2939469418293257</v>
+        <v>-0.2929102246222257</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.7012561406463007</v>
+        <v>-0.6991481104787596</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7464420672621443</v>
+        <v>-0.7441523294026737</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6185328133262118</v>
+        <v>-0.6233275692913125</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6469801249889713</v>
+        <v>-0.6337202079517326</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5959315920477053</v>
+        <v>-0.5714239986204888</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6680827065961381</v>
+        <v>-0.6433085502338898</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5512650097680023</v>
+        <v>-0.5300218675607482</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5167655832614457</v>
+        <v>-0.4987116448868534</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4073750105455858</v>
+        <v>-0.3895488969582104</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1131117113735556</v>
+        <v>-0.0992759789398292</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.02847130683038301</v>
+        <v>-0.01803466669463205</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.08657073647422209</v>
+        <v>-0.07930622435663537</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.1642</t>
+          <t>X &gt; -0.1641</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3578</v>
+        <v>3586</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4184857072344599</v>
+        <v>-0.4123068790687014</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4260859540972035</v>
+        <v>-0.4245840740228246</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.638574568029739</v>
+        <v>-0.6365959837064494</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7314392180833167</v>
+        <v>-0.714206260924847</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.696890498055815</v>
+        <v>-0.6878384515022873</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7900325074723256</v>
+        <v>-0.7616977424923235</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8189548611596891</v>
+        <v>-0.7795450622391371</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.9082714627069421</v>
+        <v>-0.8684694936953434</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.70292901096051</v>
+        <v>-0.667560836935408</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5884403823777973</v>
+        <v>-0.556996797387967</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4704741841839919</v>
+        <v>-0.4392080446673106</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1970472969632482</v>
+        <v>-0.1704153795093006</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.07066740997125009</v>
+        <v>-0.04816699025224835</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2203984868846334</v>
+        <v>-0.2016726410184475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.1368</t>
+          <t>X &gt; -0.1367</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3454</v>
+        <v>3461</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5028623198788509</v>
+        <v>-0.4951434886751187</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5392425048806757</v>
+        <v>-0.5372854548168036</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5140332887635068</v>
+        <v>-0.5123725204773564</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6727419793271281</v>
+        <v>-0.6550397168374715</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7330882068778948</v>
+        <v>-0.7253545341178409</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8403384546994559</v>
+        <v>-0.8117154443954817</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.011754016277763</v>
+        <v>-0.9722095119845875</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.103100116711893</v>
+        <v>-1.047600376476232</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.032817097526497</v>
+        <v>-0.9824228139591327</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.768167499423086</v>
+        <v>-0.7228012807411943</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6386794542280541</v>
+        <v>-0.5934434328852305</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2699187018877254</v>
+        <v>-0.2304624900529717</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1239449102957408</v>
+        <v>-0.08954981934962092</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3450746993300555</v>
+        <v>-0.3153930017329216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.1094</t>
+          <t>X &gt; -0.1093</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3312</v>
+        <v>3318</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3712113891841469</v>
+        <v>-0.3623196951182805</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1138019427663508</v>
+        <v>-0.09689467927361051</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1469096747185006</v>
+        <v>-0.1137176107110065</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4386254594001784</v>
+        <v>-0.3884116484838103</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4946968087586896</v>
+        <v>-0.4403769605007994</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8302341715286587</v>
+        <v>-0.752908525003896</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.186192270397001</v>
+        <v>-1.09830108791148</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.321735899114415</v>
+        <v>-1.216892439059244</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.185603914246727</v>
+        <v>-1.08708299372757</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.114526111923531</v>
+        <v>-1.021137482691863</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8501637052569606</v>
+        <v>-0.7869110248238655</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5576640135844571</v>
+        <v>-0.5010836105627945</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3271439031681851</v>
+        <v>-0.2633301447215501</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.5976873671324157</v>
+        <v>-0.5567807619105238</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.08201</t>
+          <t>X &gt; -0.08193</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3129</v>
+        <v>3135</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5191935424960761</v>
+        <v>-0.5075689132531664</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.05701440429993454</v>
+        <v>-0.03923485598878074</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.005214816168212622</v>
+        <v>0.02951254184601737</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2258668655623097</v>
+        <v>-0.1732421253579446</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1580958125973879</v>
+        <v>-0.1041895792532799</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.6262720221967655</v>
+        <v>-0.546226663930419</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9980637211758463</v>
+        <v>-0.908147918819779</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.305642731788737</v>
+        <v>-1.197578603812978</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.381352488771149</v>
+        <v>-1.281108728333756</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.256541322586159</v>
+        <v>-1.163319215680545</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8690318478573502</v>
+        <v>-0.8078941092296645</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3378808072380579</v>
+        <v>-0.285498618162336</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3567879908892166</v>
+        <v>-0.2978814251089332</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5924476970984642</v>
+        <v>-0.5592033892498733</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.05461</t>
+          <t>X &gt; -0.05455</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2885</v>
+        <v>2891</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.491984864847737</v>
+        <v>-0.477031190841501</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.09694473861028996</v>
+        <v>-0.07743230887083286</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.09631569953332075</v>
+        <v>0.1336627568148714</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3960810870062943</v>
+        <v>-0.3385157443453508</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.03415236231931829</v>
+        <v>0.08804554503841899</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5678163960082401</v>
+        <v>-0.4831680947401296</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6871168625037427</v>
+        <v>-0.5942073198825355</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.015825077373151</v>
+        <v>-0.9032041371748178</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.023473836728485</v>
+        <v>-0.9214494169433607</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.058513141465724</v>
+        <v>-0.966081447975732</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.724778797405051</v>
+        <v>-0.6671116551692009</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.394058363717896</v>
+        <v>-0.3476173753237859</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.136511189142773</v>
+        <v>-0.08556326453029328</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.3071310999165178</v>
+        <v>-0.2861897964962523</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.02721</t>
+          <t>X &gt; -0.02716</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9093211527695075</v>
+        <v>-0.924651654740039</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4250474088135476</v>
+        <v>-0.3988981943755334</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1213321812286523</v>
+        <v>-0.0752621924751935</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3015455320135985</v>
+        <v>-0.234030197444838</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1025436609726995</v>
+        <v>-0.04391329941159228</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4648514318808736</v>
+        <v>-0.369809501360308</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9376099091136751</v>
+        <v>-0.8358129560982164</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.327068929307082</v>
+        <v>-1.203236081114198</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.504465521219849</v>
+        <v>-1.37446126618282</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.324218999410512</v>
+        <v>-1.207307073745248</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9251391771484876</v>
+        <v>-0.8467139850060619</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.519611139080169</v>
+        <v>-0.4175498406581184</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.101941955195386</v>
+        <v>-0.03600873809572391</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1652619909143596</v>
+        <v>-0.1364784391871581</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.0001913</t>
+          <t>X &gt; 0.0002207</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.402665876498624</v>
+        <v>-1.34732112721256</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.06686275625393989</v>
+        <v>0.1014447090631023</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5963057892438215</v>
+        <v>0.6600319251718716</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1976834849127371</v>
+        <v>-0.09595340282036346</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3114699687691385</v>
+        <v>0.3683319282855919</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8082847754713001</v>
+        <v>-0.675509487256214</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.693980963449732</v>
+        <v>-1.563009497248245</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.284278196269128</v>
+        <v>-2.119148801533711</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.406874647308236</v>
+        <v>-2.246539032732393</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.484411538335699</v>
+        <v>-2.360896518836434</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.224229394741599</v>
+        <v>-2.162573912185337</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.90957919571489</v>
+        <v>-1.88629105463918</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.802045683583998</v>
+        <v>-1.78853462507238</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.975043857819919</v>
+        <v>-2.032404119187639</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.02759</t>
+          <t>X &gt; 0.02761</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.057513413136355</v>
+        <v>-1.975760679848811</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2044962729438282</v>
+        <v>-0.1589879169183206</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3683207754817843</v>
+        <v>-0.2821339319966896</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6999893963276023</v>
+        <v>-0.5698436987648989</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6092961083134298</v>
+        <v>0.6666248472344733</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.24806427313694</v>
+        <v>-0.09084785858620137</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.179579867199095</v>
+        <v>-1.029968089973707</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.569666216913475</v>
+        <v>-1.377915743312897</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.323489020087521</v>
+        <v>-2.141676232952328</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.387491445815684</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.446132357826826</v>
+        <v>-1.395806197141752</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9064927759618087</v>
+        <v>-0.9105653791231063</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.5889416415732285</v>
+        <v>-0.6128826590356624</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7835601056729899</v>
+        <v>-0.9027138555268408</v>
       </c>
     </row>
     <row r="22">
@@ -3046,101 +3046,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.573508623126948</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2032132347092954</v>
+        <v>-0.1762382187985949</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.073742765516208</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.301092809209301</v>
+        <v>-1.263883392692257</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.382839859917226</v>
+        <v>0.4216301830512421</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8938601845217562</v>
+        <v>-0.8767488082961847</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.460052025269405</v>
+        <v>-2.460349525023055</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.556750298685785</v>
+        <v>-2.463647595304643</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.099213936690042</v>
+        <v>-3.980731212767061</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.233552463222757</v>
+        <v>-3.139434909215709</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.018191755637957</v>
+        <v>-2.973547604670401</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.727317082162159</v>
+        <v>-1.755018377155785</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.539193539780513</v>
+        <v>-1.594620748164054</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.634284378704145</v>
+        <v>-1.808538849111649</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.08239</t>
+          <t>X &gt; 0.08238</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.630970795046949</v>
+        <v>-3.490503981749733</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1247653462813361</v>
+        <v>0.2142356264893337</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.80341239115716</v>
+        <v>-1.648598950759286</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.892245297952151</v>
+        <v>-1.788836846213897</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1304253220226528</v>
+        <v>-0.03238762172716037</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.037870569496</v>
+        <v>-0.9631031970001374</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.984574357020662</v>
+        <v>-2.936562678030342</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.903997874849019</v>
+        <v>-2.854750312455302</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.169799308480229</v>
+        <v>-4.096542198700533</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.661121037113467</v>
+        <v>-2.620261250490323</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.477897801513045</v>
+        <v>-2.495814622451384</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.8459514654204909</v>
+        <v>-0.9042415324030273</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5451071422931761</v>
+        <v>-0.6422253078168012</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5879776478364178</v>
+        <v>-0.8312965465681401</v>
       </c>
     </row>
     <row r="24">
@@ -3150,621 +3150,621 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.309415400017329</v>
+        <v>-4.078493255250848</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1198448726524077</v>
+        <v>0.05243973317324446</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.406167329286383</v>
+        <v>-2.285769036722321</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.528148995281889</v>
+        <v>-2.467974091399782</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6704738573309186</v>
+        <v>-0.6219279375651467</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.255823661239333</v>
+        <v>-1.23186625228972</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.232085092384452</v>
+        <v>-3.184073413394131</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.573050331379257</v>
+        <v>-3.52380276898554</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.768963131029395</v>
+        <v>-4.695706021249698</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.661253945141105</v>
+        <v>-3.627983530185745</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.788333118699676</v>
+        <v>-2.823296739386393</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.306516217124489</v>
+        <v>-2.386819787645713</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.264152430852448</v>
+        <v>-1.394840261498317</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.095032814544076</v>
+        <v>-1.39800220906681</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.1372</t>
+          <t>X &gt; 0.1371</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.615244388743307</v>
+        <v>-5.399000713775877</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.256281228075792</v>
+        <v>-0.9775619070754757</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.636127239696506</v>
+        <v>-4.412732693305536</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.953663290137996</v>
+        <v>-4.803571428571431</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.95463941039786</v>
+        <v>-2.983500790941278</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.105026574792625</v>
+        <v>-3.157809161839189</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.83152797883492</v>
+        <v>-4.857809513359733</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.552327965905242</v>
+        <v>-4.42945449430939</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.658086241831001</v>
+        <v>-5.509646179452155</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-4.341260286582425</v>
+        <v>-4.247036608255215</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.318837217960059</v>
+        <v>-4.302145759219023</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.05665380655762</v>
+        <v>-4.094947725281848</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.99606304869463</v>
+        <v>-2.105604906689194</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.68813994785959</v>
+        <v>-2.005591341246102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.1646</t>
+          <t>X &gt; 0.1645</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-6.539637964903953</v>
+        <v>-6.197933437236898</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.451342192682809</v>
+        <v>-2.203254545781661</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-5.782210295917984</v>
+        <v>-5.605787655672515</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-5.997408295680231</v>
+        <v>-5.908866995073893</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.635870560347598</v>
+        <v>-4.587324640581826</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.85663124573842</v>
+        <v>-4.832673836788807</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-6.323034178407006</v>
+        <v>-6.275022499416686</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-6.099256535492536</v>
+        <v>-6.050008973098819</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.023796550391822</v>
+        <v>-6.950539440612125</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.887233463508167</v>
+        <v>-5.874540732998781</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.31173876322309</v>
+        <v>-5.387834893833663</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-5.015289072258099</v>
+        <v>-5.15695658479347</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.259413355523201</v>
+        <v>-3.479575651253676</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.94066149563146</v>
+        <v>-3.403242360913609</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.192</t>
+          <t>X &gt; 0.1919</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-5.869006379610326</v>
+        <v>-5.463268647697575</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.730705819696738</v>
+        <v>-1.44022768555304</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.616236958045207</v>
+        <v>-5.407272297130547</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-5.691350623491758</v>
+        <v>-5.586651053864173</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.586929704308197</v>
+        <v>-4.538383784542425</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.905572101777828</v>
+        <v>-4.881614692828215</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.606298888148714</v>
+        <v>-5.558287209158394</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.457351104830735</v>
+        <v>-5.408103542437019</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.339688497493135</v>
+        <v>-6.266431387713439</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.854482527258575</v>
+        <v>-5.858227114318986</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-5.337109950844813</v>
+        <v>-5.446351134750344</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-4.577674288052414</v>
+        <v>-4.772167970280741</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.027529297552178</v>
+        <v>-3.319276615530384</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.105479978433955</v>
+        <v>-3.686248180619742</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.2194</t>
+          <t>X &gt; 0.2193</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-6.849848069369301</v>
+        <v>-6.356265671040831</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.150354550782652</v>
+        <v>-1.804132283536809</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.671339527770698</v>
+        <v>-6.41939404811599</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-6.541114384182336</v>
+        <v>-6.415254237288138</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.166782578054729</v>
+        <v>-4.118236658288957</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.325719228031289</v>
+        <v>-5.301761819081676</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.410429587297457</v>
+        <v>-5.362417908307137</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.848372017491961</v>
+        <v>-6.799124455098244</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.12294640702445</v>
+        <v>-8.049689297244754</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.641752359946089</v>
+        <v>-7.659925645050023</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.996652319464374</v>
+        <v>-7.135910752780291</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.130322351258378</v>
+        <v>-5.37871488920181</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.689933389623789</v>
+        <v>-5.045717475959812</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.582230210370909</v>
+        <v>-5.282109507148327</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.2468</t>
+          <t>X &gt; 0.2467</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.387892774720399</v>
+        <v>-4.659108959557472</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.347916077086552</v>
+        <v>-2.081794657169276</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.393850252539266</v>
+        <v>-7.224779059740825</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.263625108950905</v>
+        <v>-6.958298926507027</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.022844894604738</v>
+        <v>-3.831899244471593</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.051052260318492</v>
+        <v>-5.877954305362806</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-6.135762619584661</v>
+        <v>-5.938610394588267</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-6.893528937789995</v>
+        <v>-6.694298227435375</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-8.117301791987195</v>
+        <v>-7.890691126427249</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-7.955287575909431</v>
+        <v>-7.844954489850927</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.142137984847345</v>
+        <v>-7.179529719995713</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.204173888159048</v>
+        <v>-5.382232547848211</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.827188291584584</v>
+        <v>-3.168694822238123</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.917607421854321</v>
+        <v>-4.658780395005373</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.2742</t>
+          <t>X &gt; 0.2741</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.253965675924427</v>
+        <v>-3.918562529112336</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.609832620052082</v>
+        <v>-1.276387501592133</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.323752940977329</v>
+        <v>-7.137203576802776</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-8.966577442779041</v>
+        <v>-8.967071935157044</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-5.604157776016585</v>
+        <v>-5.555611856250813</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.789053249927591</v>
+        <v>-7.765095840977978</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-8.228373538271775</v>
+        <v>-8.180361859281454</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-8.340832252980498</v>
+        <v>-8.291584690586781</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-9.820254125815332</v>
+        <v>-9.746997016035635</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-10.31556299306718</v>
+        <v>-10.21621566777261</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.933984148298677</v>
+        <v>-9.001916398996634</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.301995421464454</v>
+        <v>-7.525309945319691</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.754660355679036</v>
+        <v>-6.14741822649345</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.7055575926911</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.3016</t>
+          <t>X &gt; 0.3015</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-5.089611682708266</v>
+        <v>-4.64686396163912</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.222536906206884</v>
+        <v>-2.811237627991559</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.834699595309743</v>
+        <v>-8.564280117241658</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-10.44360488650398</v>
+        <v>-10.39162561576355</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.503633570034467</v>
+        <v>-7.432598894646503</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-7.20625954039938</v>
+        <v>-7.159813375827575</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-7.290969899665548</v>
+        <v>-7.220469465053036</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-8.192821152147935</v>
+        <v>-8.117336708194998</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-10.42771635214897</v>
+        <v>-10.3094817311249</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-10.84285253978318</v>
+        <v>-10.70227582918126</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-9.540054172696877</v>
+        <v>-9.613312828441494</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.984952814948159</v>
+        <v>-8.262042642800736</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.430453386168665</v>
+        <v>-6.933062638330078</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-7.115052259073337</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.329</t>
+          <t>X &gt; 0.3288</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.425970975589294</v>
+        <v>-7.154920568056383</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-3.820064866326987</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-11.62973065121037</v>
+        <v>-11.31762799125372</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-12.04895605707255</v>
+        <v>-12.04945054945055</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-9.839992862915494</v>
+        <v>-9.791446943149722</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-9.542618833280407</v>
+        <v>-9.518661424330794</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-7.429526994744386</v>
+        <v>-7.381515315754065</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-7.896595638531124</v>
+        <v>-7.847348076137408</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-10.15537999285609</v>
+        <v>-10.08212288307639</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-11.5547493386365</v>
+        <v>-11.45540201334193</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.40859141123098</v>
+        <v>-10.56064136197692</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-8.452789072258099</v>
+        <v>-8.854122976260385</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.136751222902362</v>
+        <v>-4.853676507219802</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-6.986779805931747</v>
+        <v>-7.901334941907741</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.3564</t>
+          <t>X &gt; 0.3562</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.124272673890999</v>
+        <v>-8.760111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>0.07337775662382739</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.82953085101057</v>
+        <v>-11.43147134280198</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.69930570742221</v>
+        <v>-11.69980019980021</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-12.2375952605179</v>
+        <v>-12.18904934075213</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-11.94022123088281</v>
+        <v>-11.9162638219332</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.528428093645481</v>
+        <v>-8.48041641465516</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.694797436732919</v>
+        <v>-9.645549874339203</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.755779593255696</v>
+        <v>-9.682522483475999</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-12.00429978818695</v>
+        <v>-11.90495246289237</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-10.49029711506726</v>
+        <v>-10.71049151182707</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-8.712836353581977</v>
+        <v>-9.25372337586078</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-4.054475708019012</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.62642090204362</v>
+        <v>-5.903332943905738</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.3838</t>
+          <t>X &gt; 0.3836</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.51663031624864</v>
+        <v>-10.54582611060127</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.877816409312466</v>
+        <v>-5.879003195757122</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-16.98687350835322</v>
+        <v>-16.98702689835754</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-16.85664836476486</v>
+        <v>-16.85714285714286</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-15.60922363214627</v>
+        <v>-15.5606777123805</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-17.99042103108261</v>
+        <v>-17.966463622133</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-11.82513139034878</v>
+        <v>-11.77711971135846</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-14.0779143198498</v>
+        <v>-14.02866675745609</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.24603933351543</v>
+        <v>-13.17278222373574</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-16.77452955841672</v>
+        <v>-16.67518223312215</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-13.02170175914796</v>
+        <v>-13.30789410922967</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-11.68511230458133</v>
+        <v>-12.35687022900763</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.192002107019015</v>
+        <v>-7.394885298428605</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.350907979048678</v>
+        <v>-8.931554722127522</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.4112</t>
+          <t>X &gt; 0.411</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-6.473054504550568</v>
+        <v>-6.474241290995224</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-16.39163541311513</v>
+        <v>-16.39178880311945</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-15.07093407905057</v>
+        <v>-15.07142857142858</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-16.79969982262246</v>
+        <v>-16.75115390285669</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-21.26423055489214</v>
+        <v>-21.24027314594252</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-14.20608377130116</v>
+        <v>-14.15807209231084</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-13.4826762246117</v>
+        <v>-13.43342866221798</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-13.54365838113448</v>
+        <v>-13.47040127135478</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-17.96500574889291</v>
+        <v>-17.86565842359834</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-11.68663174937915</v>
+        <v>-12.11741791875348</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.669591240279779</v>
+        <v>-9.678298800436202</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.329730049028299</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.674982053122754</v>
+        <v>-5.062507103079902</v>
       </c>
     </row>
   </sheetData>
@@ -3904,833 +3904,833 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.3834</t>
+          <t>X &lt; -0.3832</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.61432206470374</v>
+        <v>10.58512627035111</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.431707400211344</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.227412205932488</v>
+        <v>6.227258815928167</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.500494492378</v>
+        <v>13.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>17.72410970118707</v>
+        <v>17.77265562095284</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>21.59291230225072</v>
+        <v>21.61686971120034</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19.12724956203218</v>
+        <v>19.1752612410225</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>17.46970472776925</v>
+        <v>17.51895229016296</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>17.40872257124647</v>
+        <v>17.48197968102617</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>19.03910348116356</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>17.54457880713261</v>
+        <v>17.64448684315128</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.38848076901174</v>
+        <v>16.51217739003999</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>15.96832991569833</v>
+        <v>16.11701946347616</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>17.38454175640106</v>
+        <v>17.55654051596772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.356</t>
+          <t>X &lt; -0.3558</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.863911555672544</v>
+        <v>7.834715761319913</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5.390656497091477</v>
+        <v>5.389469710646821</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.995885112336438</v>
+        <v>4.995731722332117</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.88473094557997</v>
+        <v>12.88423645320196</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.932648289036</v>
+        <v>14.98119420880177</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>17.8162292152228</v>
+        <v>17.84018662417242</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16.8694498904394</v>
+        <v>16.91746156942972</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.54031228113542</v>
+        <v>15.58955984352914</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.47933012461264</v>
+        <v>15.55258723439234</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>15.49148029380002</v>
+        <v>15.5908276190946</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.70057223898812</v>
+        <v>12.80048027500679</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.01081246030895</v>
+        <v>11.13450908133719</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.59066160699554</v>
+        <v>10.73935115477337</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.4026041537738</v>
+        <v>13.57460291334046</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.3286</t>
+          <t>X &lt; -0.3284</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>146</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.053330544808112</v>
+        <v>5.024134750455481</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.812007465442917</v>
+        <v>4.810820678998262</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.787099094386505</v>
+        <v>5.786945704382184</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.76663930646802</v>
+        <v>12.76614481409001</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.22834975337232</v>
+        <v>12.27689567313809</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.52572378300741</v>
+        <v>12.54968119195702</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.75608191689193</v>
+        <v>11.80409359588225</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.60408176625587</v>
+        <v>10.65332932864958</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.54309960973309</v>
+        <v>10.61635671951279</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.37811232025255</v>
+        <v>10.47745964554713</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.488479655143038</v>
+        <v>9.588387691161714</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.468063286950425</v>
+        <v>7.59175990797867</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.047912433637016</v>
+        <v>7.196601981414844</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.328442604411485</v>
+        <v>9.500441363978148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.3012</t>
+          <t>X &lt; -0.301</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.929340379722056</v>
+        <v>4.122541236337504</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.369436337940286</v>
+        <v>4.580180477712268</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.487485466005758</v>
+        <v>4.696646571030215</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.745915737799244</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.694805671883032</v>
+        <v>8.929118205986853</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>9.505000214338637</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.688859773126921</v>
+        <v>7.610635390682361</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.221791129340183</v>
+        <v>7.144802630299019</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.191736807868949</v>
+        <v>8.128238184427531</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.34181801153909</v>
+        <v>7.304409603612548</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.621652935753126</v>
+        <v>6.5900650744438</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.563247582953814</v>
+        <v>3.587007322012781</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.627632812114634</v>
+        <v>2.681645313816297</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.915224132444258</v>
+        <v>4.971506502362274</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.2738</t>
+          <t>X &lt; -0.2736</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.772002257403393</v>
+        <v>2.742806463050762</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.44097180636291</v>
+        <v>5.439785019918254</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.76993583016818</v>
+        <v>7.769782440163858</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.62389638231685</v>
+        <v>10.62340188993885</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.918291654123877</v>
+        <v>8.966837573889649</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.437455567027449</v>
+        <v>8.461412975977062</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.817725752508366</v>
+        <v>7.622546770020087</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.960032108721627</v>
+        <v>6.767608951270986</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.289674952198851</v>
+        <v>7.119741400499947</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>6.295912819684965</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>5.844429997608799</v>
+        <v>5.702667313783117</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.363183149964122</v>
+        <v>2.258888525856186</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.01009270334928658</v>
+        <v>-0.081794692536441</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.387517946877246</v>
+        <v>1.334565344576198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.2464</t>
+          <t>X &lt; -0.2462</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.710367012204294</v>
+        <v>6.709180225759638</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.710657355844312</v>
+        <v>9.71050396583999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.45816645004995</v>
+        <v>10.45767195767195</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.685308995719701</v>
+        <v>8.733854915485473</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>9.179525895056273</v>
+        <v>9.006640434304401</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.982322025800293</v>
+        <v>8.637342369770295</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.204694375802369</v>
+        <v>7.862867634078306</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.522594206857235</v>
+        <v>7.208611074324224</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.914911435372098</v>
+        <v>7.619350394743819</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.467974252267183</v>
+        <v>6.180642045973151</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.086203336299519</v>
+        <v>2.84374705494298</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.113257451930217</v>
+        <v>0.9053792518359458</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.891788133212643</v>
+        <v>2.697633990394522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.219</t>
+          <t>X &lt; -0.2189</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.706276087692252</v>
+        <v>1.677080293339621</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.297060437978175</v>
+        <v>3.295873651533519</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.335786590168944</v>
+        <v>7.335633200164622</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.712317152476523</v>
+        <v>7.71182266009852</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.435111343223191</v>
+        <v>6.483657262988963</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.390090432762186</v>
+        <v>6.263831944369464</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.198913871320244</v>
+        <v>6.942092111301648</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.236795722583011</v>
+        <v>5.983648513479878</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.928288813584992</v>
+        <v>5.700370485623864</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.563518532106613</v>
+        <v>6.354374417124149</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.87366885899494</v>
+        <v>4.672401457272791</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.937749981647286</v>
+        <v>1.77490317000715</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.022549623383384</v>
+        <v>0.8871344060048969</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.238384283510904</v>
+        <v>2.121400942897111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.1916</t>
+          <t>X &lt; -0.1915</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5678644572705309</v>
+        <v>0.5386686629178996</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.224971047133522</v>
+        <v>3.223784260688866</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.878980150183367</v>
+        <v>5.878826760179045</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.415709358812371</v>
+        <v>6.415214866434368</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.470915740676034</v>
+        <v>5.519461660441806</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.891234482446635</v>
+        <v>5.792247179260734</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.725889017814488</v>
+        <v>5.528339057514955</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.075146904639993</v>
+        <v>5.875514427212906</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.401919850158038</v>
+        <v>5.228785720515134</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.164245951787358</v>
+        <v>5.014713237261127</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.347299895567986</v>
+        <v>4.200816692164061</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.136780088739634</v>
+        <v>2.023211071805378</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.512547602773161</v>
+        <v>1.424801112721219</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.738283252999693</v>
+        <v>1.673845974736587</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.1642</t>
+          <t>X &lt; -0.1641</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.679828470311676</v>
+        <v>2.650632675959045</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.437508705505039</v>
+        <v>3.436321919060383</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.396375222611248</v>
+        <v>4.396221832606926</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.134877058963951</v>
+        <v>5.033720087019574</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.935570556715717</v>
+        <v>4.882880421532974</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.674082970857725</v>
+        <v>5.494075415817207</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.032011466794074</v>
+        <v>5.771828802057065</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>6.415282959061763</v>
+        <v>6.152019730337003</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.333892639273685</v>
+        <v>5.099818694804263</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.445194851721944</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.939136630261864</v>
+        <v>3.733440190987885</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.272834510508339</v>
+        <v>2.099559551026211</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.512547602773161</v>
+        <v>1.365992148997066</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.248487334632351</v>
+        <v>2.122651224210401</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.1368</t>
+          <t>X &lt; -0.1367</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.547016930359504</v>
+        <v>2.517821136006873</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.310132513273324</v>
+        <v>3.308945726828668</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.915361128518285</v>
+        <v>2.915207738513963</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.825169817053322</v>
+        <v>3.74341580207502</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.126041103118474</v>
+        <v>4.09215548793874</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.786189613175097</v>
+        <v>4.644270615696222</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.766533606645808</v>
+        <v>5.56126815775567</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.08661216490141</v>
+        <v>5.79375941971869</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.885180570176381</v>
+        <v>5.617122006112623</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.613913459239782</v>
+        <v>4.374299011889825</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.987863986372837</v>
+        <v>3.751164150945911</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.196399442098951</v>
+        <v>1.993688430210248</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.495349712381056</v>
+        <v>1.319200894707876</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.423332553618813</v>
+        <v>2.266569779069606</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.1094</t>
+          <t>X &lt; -0.1093</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.526052610580628</v>
+        <v>1.496856816227996</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.024176946169256</v>
+        <v>0.9589758983195367</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9263977372812349</v>
+        <v>0.797525947170918</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.170158162041666</v>
+        <v>1.972706155632984</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.397944229163954</v>
+        <v>2.180321126179315</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.813651065045562</v>
+        <v>3.498402812245637</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>4.947618964599734</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.740586851110386</v>
+        <v>5.294794334297691</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.328316638381523</v>
+        <v>4.909389669411759</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.063877935728478</v>
+        <v>4.666281181511998</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.039504646320744</v>
+        <v>3.765276622477643</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.902922611322438</v>
+        <v>2.662003174012106</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.014387683067575</v>
+        <v>1.753785797916905</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.942699445706282</v>
+        <v>2.769135449168004</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.08201</t>
+          <t>X &lt; -0.08193</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.637857915825805</v>
+        <v>1.608662121473174</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6538230921256982</v>
+        <v>0.6001976799954747</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3115909830095447</v>
+        <v>0.2064596916807702</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.070825218328324</v>
+        <v>0.9110563765736117</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.8742928513702211</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.380299441899659</v>
+        <v>2.131374363636027</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.602889529001622</v>
+        <v>3.31592900237991</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.445642643919314</v>
+        <v>4.095306969965918</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.770388549113022</v>
+        <v>4.441476123281234</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.402629829928784</v>
+        <v>4.096574745531377</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.233608517377363</v>
+        <v>3.030365332478048</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.628642407437596</v>
+        <v>1.460179579421485</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.690651631269809</v>
+        <v>1.503724481053659</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.302115343212826</v>
+        <v>2.192314211242376</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.05461</t>
+          <t>X &lt; -0.05455</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.168152292447012</v>
+        <v>1.13895649809438</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6087525772565243</v>
+        <v>0.5650961831248651</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.0232353563435197</v>
+        <v>-0.06156105984823057</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.207553969865494</v>
+        <v>1.077639751552795</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2452489980272929</v>
+        <v>0.1225521012841</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.676793087612417</v>
+        <v>1.482294141842161</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.025994083241592</v>
+        <v>1.809836810380673</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.696090363990947</v>
+        <v>2.430960571736463</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.791236232448654</v>
+        <v>2.549267465705256</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.878085586001703</v>
+        <v>2.65711590352381</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.126936340309811</v>
+        <v>1.987136946670958</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.380674367762715</v>
+        <v>1.268906168507897</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8043954894688241</v>
+        <v>0.6852290316857292</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.108195152185594</v>
+        <v>1.056503487159311</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.02721</t>
+          <t>X &lt; -0.02716</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.514090211662896</v>
+        <v>1.542257252419745</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9984662711551024</v>
+        <v>0.9565864016778605</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3881264916467728</v>
+        <v>0.3134718547596691</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.740287219975599</v>
+        <v>0.6303883149269609</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4242110183096628</v>
+        <v>0.3281715929276601</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.069311503133328</v>
+        <v>0.9126778100009574</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.896673120929414</v>
+        <v>1.724839675887715</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.468211967655797</v>
+        <v>2.256513149918341</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.819787875661838</v>
+        <v>2.593605378686775</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.53448639426297</v>
+        <v>2.330874054729648</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.890638435500897</v>
+        <v>1.752668769288327</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.23492875849611</v>
+        <v>1.062705830842738</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5638368763244941</v>
+        <v>0.4536798918396414</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6013667549073602</v>
+        <v>0.5510117126861118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.0001913</t>
+          <t>X &lt; 0.0002207</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2548</v>
+        <v>2554</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9228398380102476</v>
+        <v>0.8936440436576163</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1544732188675724</v>
+        <v>0.1320632026332262</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2582125843125027</v>
+        <v>-0.3007984163544108</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2849497550941322</v>
+        <v>0.2203219315895382</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.03600374858155675</v>
+        <v>-0.07330905599775406</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7140786049144765</v>
+        <v>0.6298364002233683</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.317725752508373</v>
+        <v>1.234282032437648</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.65724792865101</v>
+        <v>1.550921885512835</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.775546223784403</v>
+        <v>1.670443799067748</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.828296187266162</v>
+        <v>1.746458723730072</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.662841496823873</v>
+        <v>1.620565537539832</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.461740842271809</v>
+        <v>1.443990490867172</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.394808199319471</v>
+        <v>1.384468909007801</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.463557978274416</v>
+        <v>1.499561733851898</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.02759</t>
+          <t>X &lt; 0.02761</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2872</v>
+        <v>2878</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9565839694656546</v>
+        <v>0.9273881751130233</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2670503599030383</v>
+        <v>0.2469888677349417</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2733766653785423</v>
+        <v>0.2351953238646871</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4573940405184231</v>
+        <v>0.3998015873015817</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1313774171651474</v>
+        <v>-0.1588919980947807</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2893926335136641</v>
+        <v>0.2180601873908188</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7457007003162985</v>
+        <v>0.6782374314986868</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8896407495152232</v>
+        <v>0.8026824488931226</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.265998071976014</v>
+        <v>1.18237650642299</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.903544456704644</v>
+        <v>0.844659036719122</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8729380059653451</v>
+        <v>0.84885192251636</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6287646262872357</v>
+        <v>0.6292408821034741</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4871653050072595</v>
+        <v>0.496929815946423</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.5388062477128983</v>
+        <v>0.5920479781603802</v>
       </c>
     </row>
     <row r="22">
@@ -4740,101 +4740,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3091</v>
+        <v>3097</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9234079449416086</v>
+        <v>0.904836628721263</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2332690836322868</v>
+        <v>0.223721399235508</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5018252323636005</v>
+        <v>0.4743133078280266</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5852121003514199</v>
+        <v>0.5719808541973492</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.400459502169497e-05</v>
+        <v>-0.01391777129065019</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4767735390531413</v>
+        <v>0.469899804965209</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.056490705628313</v>
+        <v>1.0537812600517</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.060230200571567</v>
+        <v>1.024985264281042</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.632120762616189</v>
+        <v>1.586569598257164</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.332185790291504</v>
+        <v>1.297167997292604</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.256892590620772</v>
+        <v>1.240577748051479</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.805990898265641</v>
+        <v>0.8147173798984682</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.7417119310732261</v>
+        <v>0.7607220058229913</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7409836537682182</v>
+        <v>0.8022314303702913</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.08239</t>
+          <t>X &lt; 0.08238</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3258</v>
+        <v>3264</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.040210730029024</v>
+        <v>1.004558101763386</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1192301888061138</v>
+        <v>0.09375265474933059</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5989108053722774</v>
+        <v>0.5557603877060231</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.6540779607025016</v>
+        <v>0.6245197345441795</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1633085566949291</v>
+        <v>0.13527059359226</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4469009998456741</v>
+        <v>0.4248649361934227</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.023247224901006</v>
+        <v>1.006214349872266</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9721667742632079</v>
+        <v>0.9549505426749718</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.358121852137472</v>
+        <v>1.332800523281698</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9379145352428466</v>
+        <v>0.9240484016042032</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.886681762495229</v>
+        <v>0.8903655435754345</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.429961081210287</v>
+        <v>0.4454873949972651</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3474406760245685</v>
+        <v>0.3739289654086306</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3276269094309683</v>
+        <v>0.3953010201694056</v>
       </c>
     </row>
     <row r="24">
@@ -4844,621 +4844,621 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3378</v>
+        <v>3384</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.033555322094116</v>
+        <v>0.9823727020803048</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1767309635510088</v>
+        <v>0.136006698563115</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6549704632779907</v>
+        <v>0.6264420082148092</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.712816607153556</v>
+        <v>0.6973811628984024</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.279515068538025</v>
+        <v>0.2670769084775699</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4453228316798814</v>
+        <v>0.438185973554333</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.9390275276562932</v>
+        <v>0.9245696343886962</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9915271886269323</v>
+        <v>0.9766008363070853</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.302404377894526</v>
+        <v>1.28075442845833</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.044551892991549</v>
+        <v>1.034380930986465</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.8398507347313569</v>
+        <v>0.8470681413924623</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7262123092299575</v>
+        <v>0.7448722399823282</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4836813493446215</v>
+        <v>0.5142199980474516</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4133838438577015</v>
+        <v>0.4846053589261814</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.1372</t>
+          <t>X &lt; 0.1371</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3501</v>
+        <v>3506</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.095601495826436</v>
+        <v>1.060300692893954</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.383382483015275</v>
+        <v>0.3306086717494736</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.9736340479627188</v>
+        <v>0.9326032581147246</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.062632867408553</v>
+        <v>1.034037797195687</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6828081591722537</v>
+        <v>0.6870361669123355</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.7391941026421165</v>
+        <v>0.747964380143614</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.098485101637685</v>
+        <v>1.101575746329317</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.018561163547439</v>
+        <v>0.9932987485640865</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.259255072164578</v>
+        <v>1.22863983754106</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.009164896228889</v>
+        <v>0.9906704327305249</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.004406611433424</v>
+        <v>1.002247160159243</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9530949608752906</v>
+        <v>0.9626850731588448</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.561507375199696</v>
+        <v>0.5838001877419146</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4730470814102361</v>
+        <v>0.5353795130611374</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.1646</t>
+          <t>X &lt; 0.1645</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3592</v>
+        <v>3598</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.074639525021205</v>
+        <v>1.024681632279638</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5341829555904809</v>
+        <v>0.4950116167106913</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.016183745676798</v>
+        <v>0.9884374764691799</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.078436428118103</v>
+        <v>1.062873777179291</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.8614580776900596</v>
+        <v>0.8508633387502371</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.9239938308287705</v>
+        <v>0.9172421064146619</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.188621690182266</v>
+        <v>1.177110524425174</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.126749510614189</v>
+        <v>1.115220986320679</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.304151566898177</v>
+        <v>1.288133283183107</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.12238421822979</v>
+        <v>1.118503814311822</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.029041634579848</v>
+        <v>1.041294608190093</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.9799008559774904</v>
+        <v>1.004240882103481</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.6989482209268871</v>
+        <v>0.7360935449008963</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.6184477909752388</v>
+        <v>0.6953213201181683</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.192</t>
+          <t>X &lt; 0.1919</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3684</v>
+        <v>3690</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7964404158361731</v>
+        <v>0.7475253743560515</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3646846550525851</v>
+        <v>0.3268246341582923</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.8247796081779484</v>
+        <v>0.7981853211612417</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.861567954020714</v>
+        <v>0.8469663615649026</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.7178603467815279</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.786216963415427</v>
+        <v>0.78063905885287</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.9064398056825382</v>
+        <v>0.897249468285267</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.8615119255465871</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.005744441883976</v>
+        <v>0.9928373393804364</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9430134848592218</v>
+        <v>0.9421895667076967</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.8740343678585276</v>
+        <v>0.888848763386477</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.7726904789543525</v>
+        <v>0.7999553397897685</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5696948916561482</v>
+        <v>0.6098656401478593</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5511308676155764</v>
+        <v>0.6304855411322521</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.2194</t>
+          <t>X &lt; 0.2193</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3759</v>
+        <v>3765</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7710085779073808</v>
+        <v>0.7225325842280128</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.3688644191527501</v>
+        <v>0.331724338499825</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.8119312725232746</v>
+        <v>0.7858930804447866</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8240105087739309</v>
+        <v>0.8097887803770192</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.5661303787113283</v>
+        <v>0.5590134073106228</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.7187572175693191</v>
+        <v>0.7139630940080011</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7551094270630045</v>
+        <v>0.7474977708412069</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8878911512748218</v>
+        <v>0.8797508657586803</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.05463903839199</v>
+        <v>1.043303414763692</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.002804839029402</v>
+        <v>1.003815606395719</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.9311177802637616</v>
+        <v>0.947489572905603</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.7260705535289063</v>
+        <v>0.7553543528877711</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.6783591788002212</v>
+        <v>0.7204891041205244</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.6380666300376561</v>
+        <v>0.7191282602287714</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.2468</t>
+          <t>X &lt; 0.2467</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3827</v>
+        <v>3832</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5047423788528747</v>
+        <v>0.4448478210385503</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.3419093526668178</v>
+        <v>0.319624393784288</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.7440161342243954</v>
+        <v>0.7329678946651086</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7581741822080019</v>
+        <v>0.7326775021385785</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.4691967728207374</v>
+        <v>0.4517074551726026</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.6765875478058589</v>
+        <v>0.6607685207241474</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.7107787689617524</v>
+        <v>0.6926454804697784</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.754523357415458</v>
+        <v>0.7362777821106548</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.8910598489848525</v>
+        <v>0.8702294297137598</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.8773051498590618</v>
+        <v>0.8691347637495923</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.8032546317870057</v>
+        <v>0.8101911952963192</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.6285917598413135</v>
+        <v>0.6484766671843403</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.4174819308289202</v>
+        <v>0.4507503469070144</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.4864368128296945</v>
+        <v>0.5580814246067476</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.2742</t>
+          <t>X &lt; 0.2741</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3888</v>
+        <v>3895</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3289377031069094</v>
+        <v>0.3060684106480878</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.245680217264244</v>
+        <v>0.2216918838111894</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.6094037702090347</v>
+        <v>0.5961997341648697</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.7537779321021176</v>
+        <v>0.7516919700018221</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.5122031044872557</v>
+        <v>0.5070916084625949</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.69534464209314</v>
+        <v>0.6915741510085383</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.7533464155769849</v>
+        <v>0.7475928902377902</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.7375465688758709</v>
+        <v>0.7317426613742484</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.8709297734896637</v>
+        <v>0.8629320619785545</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.9099207649224894</v>
+        <v>0.8998370025793179</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.8081002650985099</v>
+        <v>0.8129004374242896</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.6881574297995101</v>
+        <v>0.7060627963965231</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.5766485517947402</v>
+        <v>0.6078281072622218</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5451825559307437</v>
+        <v>0.5891219696017984</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.3016</t>
+          <t>X &lt; 0.3015</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3940</v>
+        <v>3945</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3172607230741562</v>
+        <v>0.2957526847186784</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3151927092285689</v>
+        <v>0.2935631759242909</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.592933940341986</v>
+        <v>0.5825053393162918</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7117753554581583</v>
+        <v>0.712389380530972</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.5423244395539015</v>
+        <v>0.5405579260326903</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.5494949353039473</v>
+        <v>0.5490851473368465</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.5802162419833792</v>
+        <v>0.578288038786134</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.6091553329732804</v>
+        <v>0.6073205152054442</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.765315652528713</v>
+        <v>0.7616662391937368</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.7925480340415874</v>
+        <v>0.7876474163370233</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.7147504290808797</v>
+        <v>0.7245273700003168</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.6222250281367181</v>
+        <v>0.645093287587251</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.5320234134019799</v>
+        <v>0.5684229341396474</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.5039519570295354</v>
+        <v>0.5531003566340189</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.329</t>
+          <t>X &lt; 0.3288</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3988</v>
+        <v>3995</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.3587136917573588</v>
+        <v>0.3473875512048608</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3123022808062217</v>
+        <v>0.3001209751294027</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6069938258144916</v>
+        <v>0.5941216659370951</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.6508629021354935</v>
+        <v>0.6490993401105669</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5520943886758829</v>
+        <v>0.5482133965106115</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5627567530571014</v>
+        <v>0.5600432834021447</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4918675716013254</v>
+        <v>0.4881762121083852</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.4897548530825233</v>
+        <v>0.4860081452468066</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.6182034054452785</v>
+        <v>0.6129320619785474</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.6849918629903584</v>
+        <v>0.6782632711110566</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.6307420587923502</v>
+        <v>0.6383647344778964</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.5397440827625175</v>
+        <v>0.5606303964614696</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3452702605423852</v>
+        <v>0.3798537263104222</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4456297823837687</v>
+        <v>0.4929491219633064</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.3564</t>
+          <t>X &lt; 0.3562</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4027</v>
+        <v>4034</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.3436627603477049</v>
+        <v>0.3322015710596347</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1334245182853309</v>
+        <v>0.121791436063468</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4957739879283949</v>
+        <v>0.4832995111380072</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.5156551313918456</v>
+        <v>0.5142715840045184</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5366097011870608</v>
+        <v>0.5332765648535229</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.5500421648630933</v>
+        <v>0.5476206360136118</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4542021793073729</v>
+        <v>0.451112338699879</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4723994765548341</v>
+        <v>0.4692116018084178</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.4997047436586328</v>
+        <v>0.4955143843355643</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.5824181871577991</v>
+        <v>0.576993525740086</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.5267113174498732</v>
+        <v>0.5354832218860821</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.461759944103683</v>
+        <v>0.4838136163838413</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2651005236186776</v>
+        <v>0.3009458221237082</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2921771224421832</v>
+        <v>0.3409681194334908</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.3838</t>
+          <t>X &lt; 0.3836</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4058</v>
+        <v>4065</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.309838825624972</v>
+        <v>0.309897983842788</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2856647234259171</v>
+        <v>0.2849303688386939</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5438767991498565</v>
+        <v>0.5424137297091889</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.5646114777548306</v>
+        <v>0.5631025416301441</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.5320864483712953</v>
+        <v>0.5291602846739991</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.6215400014840355</v>
+        <v>0.6191261502355658</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.476553627416024</v>
+        <v>0.4737924413218764</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.5156817392634991</v>
+        <v>0.5127762014518709</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.517686777771651</v>
+        <v>0.5140377130841927</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6179227403933822</v>
+        <v>0.6132003108514468</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.511792306628017</v>
+        <v>0.5212953836766374</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.4722424156122216</v>
+        <v>0.4950476465763387</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3231610546595789</v>
+        <v>0.3597524642022805</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3271125747727552</v>
+        <v>0.3767830041068834</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.4112</t>
+          <t>X &lt; 0.411</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4086</v>
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1442365946182775</v>
+        <v>0.1445399042898288</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.255723963358335</v>
+        <v>0.2550667537817617</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4117338700977911</v>
+        <v>0.410633920355906</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4087475296632874</v>
+        <v>0.4076633821942082</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.4460545045300606</v>
+        <v>0.4437103909837177</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.5613603171535146</v>
+        <v>0.5592879367202528</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.4412278312562208</v>
+        <v>0.4389081632060083</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.4034946821071443</v>
+        <v>0.4012464617959992</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.4295085709901443</v>
+        <v>0.4266216666637561</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.5232118582674232</v>
+        <v>0.5194549578538243</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.3919321390674355</v>
+        <v>0.4023458461274743</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3284150393424881</v>
+        <v>0.3522262300888244</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2019499422699056</v>
+        <v>0.2395448781364138</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1829474622957434</v>
+        <v>0.2337012898790434</v>
       </c>
     </row>
   </sheetData>
